--- a/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
+++ b/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bulkfiles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="bulkfiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="metadatos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -94,11 +94,79 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -113,13 +181,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -128,7 +196,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -143,13 +211,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -158,7 +226,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -173,13 +241,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>

--- a/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
+++ b/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V107"/>
+  <dimension ref="A1:V105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -713,15 +713,15 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServICT</t>
+          <t>US.DigitallyDeliverableServices</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1922</v>
+        <v>1948</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>International trade in ICT services, value, shares and growth, annual</t>
+          <t>Digitally deliverable services: Trade – Annual (analytical)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>ICT, information, communication, technology, services, exports, imports, trade;</t>
+          <t>digital, digitally, deliverable, information, communication, technology, services, exports, imports, trade</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>2025-09-26T12:05:00</t>
+          <t>2025-09-26T12:02:00</t>
         </is>
       </c>
       <c r="J7" s="5" t="n">
@@ -754,19 +754,19 @@
         <v>0</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>141178</v>
+        <v>1525091</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>94</v>
+        <v>577</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -809,15 +809,15 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>US.DigitallyDeliverableServices</t>
+          <t>US.TradeServICT</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1948</v>
+        <v>1922</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>International trade in digitally deliverable services, value, shares and growth, annual (analytical)</t>
+          <t>ICT services: Trade – Annual</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>digital, digitally, deliverable, information, communication, technology, services, exports, imports, trade</t>
+          <t>ICT, information, communication, technology, services, exports, imports, trade;</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>2025-09-26T12:02:00</t>
+          <t>2025-09-26T12:05:00</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
@@ -850,19 +850,19 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>1525091</v>
+        <v>141178</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>577</v>
+        <v>94</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -2153,15 +2153,15 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchProdConcent</t>
+          <t>US.BiotradeMerchShare</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>2120</v>
+        <v>2516</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Product concentration indices of exports and imports, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade as percentage of total trade - Annual (analytical)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Export, import, merchandise, trade, product concentration, biotrade, biodiversity</t>
+          <t>Export, import, value, share, merchandise, trade, biotrade, biodiversity</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>2025-11-28T16:02:00</t>
+          <t>2026-07-20T06:30:00</t>
         </is>
       </c>
       <c r="J22" s="5" t="n">
@@ -2194,10 +2194,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>34933</v>
+        <v>12702448</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>8</v>
+        <v>6710</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
@@ -2249,20 +2249,20 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>US.BiotradeMerchRCA</t>
+          <t>US.BioTradeMerchProdConcent</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Revealed comparative advantage index, annual (analytical)</t>
+          <t>Biotrade: Product concentration index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Merchandise biotrade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Export, import, merchandise, trade, Revealed Comparative Advantage, RCA, biotrade, biodiversity</t>
+          <t>Export, import, merchandise, trade, product concentration, biotrade, biodiversity</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>20785250</v>
+        <v>34933</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>2635</v>
+        <v>8</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchGDPShare</t>
+          <t>US.BiotradeMerchRCA</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Trade and biodiversity - Biotrade as percentage of Gross Domestic Product, annual (analytical)</t>
+          <t>Biotrade: Revealed Comparative Advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>Merchandise biotrade</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Export, import, share, GDP, merchandise, trade, biotrade, biodiversity</t>
+          <t>Export, import, merchandise, trade, Revealed Comparative Advantage, RCA, biotrade, biodiversity</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2386,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>21192</v>
+        <v>20785250</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>4</v>
+        <v>2635</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
@@ -2441,15 +2441,15 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>US.BiotradeMerchShare</t>
+          <t>US.BioTradeMerchGDPShare</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2122</v>
+        <v>2513</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Trade and biodiversity - Biotrade as percentage of total trade, annual (analytical)</t>
+          <t>Biotrade: Trade as percentage of Gross Domestic Product - Annual (analytical)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Export, import, value, share, merchandise, trade, biotrade, biodiversity</t>
+          <t>Export, import, share, GDP, merchandise, trade, biotrade, biodiversity</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>2025-11-28T16:02:00</t>
+          <t>2026-07-20T06:30:00</t>
         </is>
       </c>
       <c r="J25" s="5" t="n">
@@ -2482,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>12097505</v>
+        <v>21748</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>6523</v>
+        <v>4</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
@@ -3305,20 +3305,20 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>US.ConcentDiversIndices</t>
+          <t>US.RCA</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>2464</v>
+        <v>1973</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Product concentration and diversification indices - Annual (analytical)</t>
+          <t>Merchandise: Revealed Comparative Advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>Trade indicators</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Concentration index, diversification index, number of commodities</t>
+          <t>Revealed comparative advantage index</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09T11:36:00</t>
+          <t>2025-11-04T13:38:00</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
@@ -3346,10 +3346,10 @@
         <v>0</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>189457</v>
+        <v>8636215</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>186</v>
+        <v>7519</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q34" s="4" t="inlineStr">
@@ -3401,20 +3401,20 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>US.RCA</t>
+          <t>US.ConcentDiversIndices</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1973</v>
+        <v>2464</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Revealed Comparative Advantage index - Annual (analytical)</t>
+          <t>Merchandise: Standard product concentration and diversification indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Trade indicators</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Revealed comparative advantage index</t>
+          <t>Concentration index, diversification index, number of commodities</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>2025-11-04T13:38:00</t>
+          <t>2026-07-09T11:36:00</t>
         </is>
       </c>
       <c r="J35" s="5" t="n">
@@ -3442,10 +3442,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>8636215</v>
+        <v>189457</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>7519</v>
+        <v>186</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1993</v>
+        <v>2512</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>2025-11-03T15:38:00</t>
+          <t>2026-07-20T11:13:00</t>
         </is>
       </c>
       <c r="J39" s="5" t="n">
@@ -3826,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>282378</v>
+        <v>304595</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q39" s="4" t="inlineStr">
@@ -4073,15 +4073,15 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatQuarterlyAnnualized</t>
+          <t>US.TradeServCatTotal</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>2230</v>
+        <v>2544</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Services (BPM6), Preliminary annual estimates based on quarterly data: Exports and imports by main service-category</t>
+          <t>Services: Trade by category - Annual</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>services, exports, imports, trade, transport, travel, sector, category, commercial, preliminary</t>
+          <t>services, exports, imports, trade, transport, travel, sector, category</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19T10:32:00</t>
+          <t>2026-07-23T11:34:00</t>
         </is>
       </c>
       <c r="J42" s="5" t="n">
@@ -4114,19 +4114,19 @@
         <v>0</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>1379565</v>
+        <v>10102418</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>817</v>
+        <v>4793</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q42" s="4" t="inlineStr">
@@ -4169,15 +4169,15 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatTotal</t>
+          <t>US.TotAndComServicesQuarterly</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1863</v>
+        <v>2541</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Services (BPM6): Exports and imports by service category, trading partner world, annual</t>
+          <t>Services: Trade by main category - Quarterly</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>services, exports, imports, trade, transport, travel, sector, category</t>
+          <t>Services, exports, imports, seasonal, adjustment, trade, transport, travel, quarterly, growth, BPM6</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>2025-07-25T11:25:00</t>
+          <t>2026-07-23T09:54:00</t>
         </is>
       </c>
       <c r="J43" s="5" t="n">
@@ -4210,19 +4210,19 @@
         <v>0</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>9743849</v>
+        <v>4997704</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>4784</v>
+        <v>3610</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2005Q01</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2018Q02</t>
         </is>
       </c>
       <c r="Q43" s="4" t="inlineStr">
@@ -4265,35 +4265,35 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>US.TotAndComServicesQuarterly</t>
+          <t>US.ContPortThroughput</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>2272</v>
+        <v>2263</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Services: Trade by main category - Quarterly</t>
+          <t>Container port throughput, annual (analytical)</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>Maritime transport</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in services</t>
+          <t>Maritime and other transport &gt; Freight volumes by sea</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Services, exports, imports, seasonal, adjustment, trade, transport, travel, quarterly, growth, BPM6</t>
+          <t>ship, maritime, transport, container, port, throughput, TEU</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23T12:21:00</t>
+          <t>2026-04-15T15:06:00</t>
         </is>
       </c>
       <c r="J44" s="5" t="n">
@@ -4306,19 +4306,19 @@
         <v>0</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>4712785</v>
+        <v>16188</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>3610</v>
+        <v>12</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>2005Q01</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2018Q02</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q44" s="4" t="inlineStr">
@@ -4361,15 +4361,15 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>US.ContPortThroughput</t>
+          <t>US.SeaborneTrade</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>2263</v>
+        <v>2231</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Container port throughput, annual (analytical)</t>
+          <t>World seaborne trade by type of cargo, annual (analytical)</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>ship, maritime, transport, container, port, throughput, TEU</t>
+          <t>seaborne, international, maritime, trade, cargo, volume</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>2026-04-15T15:06:00</t>
+          <t>2026-03-17T15:55:00</t>
         </is>
       </c>
       <c r="J45" s="5" t="n">
@@ -4402,19 +4402,19 @@
         <v>0</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>16188</v>
+        <v>462110</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>12</v>
+        <v>225</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q45" s="4" t="inlineStr">
@@ -4457,15 +4457,15 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>US.SeaborneTrade</t>
+          <t>US.LSBCI</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>2231</v>
+        <v>2474</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>World seaborne trade by type of cargo, annual (analytical)</t>
+          <t>Liner shipping: Bilateral connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -4475,17 +4475,17 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Freight volumes by sea</t>
+          <t>Maritime and other transport &gt; Maritime connectivity</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>seaborne, international, maritime, trade, cargo, volume</t>
+          <t>Fleet, merchant, transport, maritime, ship, ports, connectivity, connections, index</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17T15:55:00</t>
+          <t>2026-06-26T14:38:00</t>
         </is>
       </c>
       <c r="J46" s="5" t="n">
@@ -4498,19 +4498,19 @@
         <v>0</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>462110</v>
+        <v>3456483</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>225</v>
+        <v>7398</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2006Q01</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026Q01</t>
         </is>
       </c>
       <c r="Q46" s="4" t="inlineStr">
@@ -4553,15 +4553,15 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>US.LSBCI</t>
+          <t>US.LSCI_M</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>2474</v>
+        <v>2458</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Bilateral connectivity index - Quarterly (analytical)</t>
+          <t>Liner shipping: Connectivity index - Monthly (analytical)</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Fleet, merchant, transport, maritime, ship, ports, connectivity, connections, index</t>
+          <t>maritime, transport, connectivity, ports, index</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26T14:38:00</t>
+          <t>2026-06-23T14:11:00</t>
         </is>
       </c>
       <c r="J47" s="5" t="n">
@@ -4594,19 +4594,19 @@
         <v>0</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>3456483</v>
+        <v>209318</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>7398</v>
+        <v>249</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>2006Q01</t>
+          <t>2006M02</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026Q01</t>
+          <t>2026M06</t>
         </is>
       </c>
       <c r="Q47" s="4" t="inlineStr">
@@ -4649,15 +4649,15 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>US.LSCI_M</t>
+          <t>US.LSCI</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Connectivity index - Monthly (analytical)</t>
+          <t>Liner shipping: Connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -4690,19 +4690,19 @@
         <v>0</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>209318</v>
+        <v>203416</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>249</v>
+        <v>323</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>2006M02</t>
+          <t>2006Q01</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026M06</t>
+          <t>2026Q02</t>
         </is>
       </c>
       <c r="Q48" s="4" t="inlineStr">
@@ -4745,15 +4745,15 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>US.LSCI</t>
+          <t>US.PLSCI</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>2457</v>
+        <v>2282</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Connectivity index - Quarterly (analytical)</t>
+          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23T14:11:00</t>
+          <t>2026-06-26T14:20:00</t>
         </is>
       </c>
       <c r="J49" s="5" t="n">
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>203416</v>
+        <v>355602</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>323</v>
+        <v>716</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
@@ -4841,15 +4841,15 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>US.PLSCI</t>
+          <t>US.VesselValueByOwnership</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2282</v>
+        <v>2338</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
+          <t>Merchant fleet: World fleet by beneficial ownership - Annual (analytical)</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -4859,17 +4859,17 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Maritime connectivity</t>
+          <t>Maritime and other transport &gt; Merchant fleet</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>maritime, transport, connectivity, ports, index</t>
+          <t>beneficial, owner, flag, merchant, fleet, maritime, transport</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26T14:20:00</t>
+          <t>2026-06-18T13:52:00</t>
         </is>
       </c>
       <c r="J50" s="5" t="n">
@@ -4882,19 +4882,19 @@
         <v>0</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>355602</v>
+        <v>9851</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>716</v>
+        <v>8</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>2006Q01</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026Q02</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="Q50" s="4" t="inlineStr">
@@ -4937,15 +4937,15 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>US.VesselValueByOwnership</t>
+          <t>US.FleetBeneficialOwners</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by beneficial ownership - Annual (analytical)</t>
+          <t>Merchant fleet: World fleet by beneficial ownership - Core indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -4978,14 +4978,14 @@
         <v>0</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>9851</v>
+        <v>412428</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>8</v>
+        <v>897</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5033,15 +5033,15 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>US.FleetBeneficialOwners</t>
+          <t>US.VesselValueByRegistration</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by beneficial ownership - Core indicators - Annual (analytical)</t>
+          <t>Merchant fleet: World fleet by flag of registration - Annual (analytical)</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -5074,14 +5074,14 @@
         <v>0</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>412428</v>
+        <v>9782</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>897</v>
+        <v>8</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
@@ -5129,15 +5129,15 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>US.VesselValueByRegistration</t>
+          <t>US.MerchantFleet</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>2339</v>
+        <v>2353</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by flag of registration - Annual (analytical)</t>
+          <t>Merchant fleet: World fleet by flag of registration and ship type - Core indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>beneficial, owner, flag, merchant, fleet, maritime, transport</t>
+          <t>merchant, fleet, maritime, transport, container, tanker, bulk, cargo, ship</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18T13:52:00</t>
+          <t>2026-06-18T13:50:00</t>
         </is>
       </c>
       <c r="J53" s="5" t="n">
@@ -5170,14 +5170,14 @@
         <v>0</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>9782</v>
+        <v>938045</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>8</v>
+        <v>1102</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -5225,15 +5225,15 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>US.MerchantFleet</t>
+          <t>US.Seafarers</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>2353</v>
+        <v>981</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by flag of registration and ship type - Core indicators - Annual (analytical)</t>
+          <t>Seafarer supply, quinquennial, 2015 and 2021 (analytical)</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -5243,17 +5243,17 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Merchant fleet</t>
+          <t>Maritime and other transport &gt; Seafarer supply</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>merchant, fleet, maritime, transport, container, tanker, bulk, cargo, ship</t>
+          <t>Seafarer, officers, ratings, nationality</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18T13:50:00</t>
+          <t>2023-07-18T11:00:00</t>
         </is>
       </c>
       <c r="J54" s="5" t="n">
@@ -5266,19 +5266,19 @@
         <v>0</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>938045</v>
+        <v>11519</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>1102</v>
+        <v>12</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q54" s="4" t="inlineStr">
@@ -5321,15 +5321,15 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>US.Seafarers</t>
+          <t>US.ShipBuilding</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>981</v>
+        <v>2439</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Seafarer supply, quinquennial, 2015 and 2021 (analytical)</t>
+          <t>Ship building: Merchant fleet built - Annual (analytical)</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Seafarer supply</t>
+          <t>Maritime and other transport &gt; Ship building and recycling</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Seafarer, officers, ratings, nationality</t>
+          <t>ship,building</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>2023-07-18T11:00:00</t>
+          <t>2026-06-18T13:48:00</t>
         </is>
       </c>
       <c r="J55" s="5" t="n">
@@ -5362,19 +5362,19 @@
         <v>0</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>11519</v>
+        <v>11070</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q55" s="4" t="inlineStr">
@@ -5417,15 +5417,15 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>US.ShipBuilding</t>
+          <t>US.ShipScrapping</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Ship building: Merchant fleet built - Annual (analytical)</t>
+          <t>Ship recycling: Merchant fleet recycled - Annual (analytical)</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>ship,building</t>
+          <t>Merchant fleet, ship, scrapping, demolition</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -5458,14 +5458,14 @@
         <v>0</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>11070</v>
+        <v>8908</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
@@ -5513,35 +5513,35 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>US.ShipScrapping</t>
+          <t>US.Gender_TradableIndustries</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>2440</v>
+        <v>1312</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Ship recycling: Merchant fleet recycled - Annual (analytical)</t>
+          <t>Employment and average monthly earnings in tradable and non-tradable industries (analytical)</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Maritime transport</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Ship building and recycling</t>
+          <t>Population and inclusiveness &gt; Gender and trade</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet, ship, scrapping, demolition</t>
+          <t>Trade, gender, employment, earnings, wages, inequality, female, male</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18T13:48:00</t>
+          <t>2024-10-10T12:39:00</t>
         </is>
       </c>
       <c r="J57" s="5" t="n">
@@ -5554,19 +5554,19 @@
         <v>0</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>8908</v>
+        <v>176441</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="Q57" s="4" t="inlineStr">
@@ -5609,35 +5609,35 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_TradableIndustries</t>
+          <t>US.PopDependency</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>1312</v>
+        <v>2331</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Employment and average monthly earnings in tradable and non-tradable industries (analytical)</t>
+          <t>Population: Dependency ratios - Annual</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Population and inclusiveness</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness &gt; Gender and trade</t>
+          <t>Population and inclusiveness &gt; Population</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Trade, gender, employment, earnings, wages, inequality, female, male</t>
+          <t>dependency, total, child, youth, old-age, elderly</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>2024-10-10T12:39:00</t>
+          <t>2026-05-21T18:32:00</t>
         </is>
       </c>
       <c r="J58" s="5" t="n">
@@ -5650,19 +5650,19 @@
         <v>0</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>176441</v>
+        <v>494161</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="Q58" s="4" t="inlineStr">
@@ -5705,15 +5705,15 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>US.PopDependency</t>
+          <t>US.PopAgeStruct</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Population: Dependency ratios - Annual</t>
+          <t>Population: Structure by gender and age group - Annual</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>dependency, total, child, youth, old-age, elderly</t>
+          <t>population, structure, gender, age</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>494161</v>
+        <v>12550832</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>303</v>
+        <v>6666</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
@@ -5801,15 +5801,15 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>US.PopAgeStruct</t>
+          <t>US.PopTotal</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Population: Structure by gender and age group - Annual</t>
+          <t>Population: Total - Annual</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>population, structure, gender, age</t>
+          <t>Population, urban, population growth rate</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -5842,10 +5842,10 @@
         <v>0</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>12550832</v>
+        <v>374021</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>6666</v>
+        <v>302</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
@@ -5897,35 +5897,35 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>US.PopTotal</t>
+          <t>US.SDG_PORFVOL</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>2329</v>
+        <v>2264</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Population: Total - Annual</t>
+          <t>Indicator 9.1.2: Container port traffic, maritime transport (twenty-foot equivalent units – TEUs) [IS_RDP_PORFVOL]</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness &gt; Population</t>
+          <t>SDG Indicators &gt; Goal 9</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Population, urban, population growth rate</t>
+          <t>ship, maritime, transport, container, port, throughput, TEU, SDG Indicator, SDG Goal 9, Indicator 9.1.2</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T18:32:00</t>
+          <t>2026-04-15T15:06:00</t>
         </is>
       </c>
       <c r="J61" s="5" t="n">
@@ -5938,19 +5938,19 @@
         <v>0</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>374021</v>
+        <v>15386</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>302</v>
+        <v>12</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q61" s="4" t="inlineStr">
@@ -5993,20 +5993,20 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>US.SDG_PORFVOL</t>
+          <t>US.SDG_LULFRG</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>2264</v>
+        <v>2254</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2, Container port traffic, maritime transport (twenty-foot equivalent units – TEUs) [IS_RDP_PORFVOL]</t>
+          <t>Indicator 9.1.2: Freight loaded and unloaded, maritime transport (metric tons) [IS_RDP_LULFRG]</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>SDG Indicators</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>ship, maritime, transport, container, port, throughput, TEU, SDG Indicator, SDG Goal 9, Indicator 9.1.2</t>
+          <t>seaborne, international, maritime, trade, cargo, volume, SDG Indicator, SDG Goal 9, Indicator 9.1.2</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-15T15:06:00</t>
+          <t>2026-04-16T07:41:00</t>
         </is>
       </c>
       <c r="J62" s="5" t="n">
@@ -6034,19 +6034,19 @@
         <v>0</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>15386</v>
+        <v>46857</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q62" s="4" t="inlineStr">
@@ -6089,65 +6089,57 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>US.SDG_LULFRG</t>
+          <t>US.IctGoods</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>2254</v>
+        <v>2533</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2, Freight loaded and unloaded, maritime transport (metric tons) [IS_RDP_LULFRG]</t>
+          <t>ICT goods: Bilateral trade by category - Annual</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>SDG Indicators</t>
+          <t>Digital economy</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>SDG Indicators &gt; Goal 9</t>
+          <t>Digital economy and technology &gt; Digital economy</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>seaborne, international, maritime, trade, cargo, volume, SDG Indicator, SDG Goal 9, Indicator 9.1.2</t>
+          <t>Digital Economy, Information Economy, International Trade, ICT goods, Imports, Exports, share, bilateral flows</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>2026-04-16T07:41:00</t>
+          <t>2025-12-01T13:16:00</t>
         </is>
       </c>
       <c r="J63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>46857</v>
+        <v>115739203</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="O63" s="4" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="P63" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O63" s="4" t="inlineStr"/>
+      <c r="P63" s="4" t="inlineStr"/>
       <c r="Q63" s="4" t="inlineStr">
         <is>
-          <t>Con valores para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R63" s="4" t="inlineStr"/>
@@ -6185,15 +6177,15 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>US.IctGoodsValue</t>
+          <t>US.IctProductionSector</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>2051</v>
+        <v>2238</v>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bilateral trade flows by ICT goods categories, annual</t>
+          <t>ICT producing sector: Workforce involved and value added - Annual</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -6208,25 +6200,25 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Digital Economy, Information Economy, International Trade, ICT goods, Imports, Exports, bilateral flows</t>
+          <t>ICT producing sector, employment, value added</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>2025-12-01T13:06:00</t>
+          <t>2026-04-20T14:48:00</t>
         </is>
       </c>
       <c r="J64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>91267142</v>
+        <v>6495</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>0</v>
@@ -6235,7 +6227,7 @@
       <c r="P64" s="4" t="inlineStr"/>
       <c r="Q64" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R64" s="4" t="inlineStr"/>
@@ -6273,15 +6265,15 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEnterprSize</t>
+          <t>US.IctUseEconActivity</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>2266</v>
+        <v>2114</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Core indicators on ICT use in business by enterprise size class, annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 3.1) - Annual</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -6296,12 +6288,12 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, enterprise size</t>
+          <t>ICT indicators, Industrial Classification, economic activity, ISIC</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T14:49:00</t>
+          <t>2025-12-08T09:44:00</t>
         </is>
       </c>
       <c r="J65" s="5" t="n">
@@ -6314,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>222567</v>
+        <v>83239</v>
       </c>
       <c r="N65" s="5" t="n">
         <v>0</v>
@@ -6361,20 +6353,20 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity</t>
+          <t>US.IctUseEconActivity_Isic4</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>2114</v>
+        <v>2250</v>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Core indicators on ICT use in business by industrial classification of economic activity (ISIC Rev. 3.1), annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 4) - Annual</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Information Economy</t>
+          <t>Information economy</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -6384,12 +6376,12 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, Industrial Classification, economic activity, ISIC</t>
+          <t>ICT indicators, industrial classification, economic activity, ISIC</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08T09:44:00</t>
+          <t>2026-04-20T14:52:00</t>
         </is>
       </c>
       <c r="J66" s="5" t="n">
@@ -6402,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>83239</v>
+        <v>663946</v>
       </c>
       <c r="N66" s="5" t="n">
         <v>0</v>
@@ -6449,20 +6441,20 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity_Isic4</t>
+          <t>US.IctUseEnterprSize</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>2250</v>
+        <v>2266</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Core indicators on ICT use in business by industrial classification of economic activity (ISIC Rev. 4), annual</t>
+          <t>ICT use in business: Core indicators by enterprise size - Annual</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Information economy</t>
+          <t>Information Economy</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -6472,12 +6464,12 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, industrial classification, economic activity, ISIC</t>
+          <t>ICT indicators, enterprise size</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T14:52:00</t>
+          <t>2026-04-20T14:49:00</t>
         </is>
       </c>
       <c r="J67" s="5" t="n">
@@ -6490,7 +6482,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>663946</v>
+        <v>222567</v>
       </c>
       <c r="N67" s="5" t="n">
         <v>0</v>
@@ -6545,7 +6537,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Core indicators on ICT use in business by location type, annual</t>
+          <t>ICT use in business: Core indicators by location type - Annual</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -6625,35 +6617,35 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>US.IctProductionSector</t>
+          <t>US.ECommerceTotal</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>2238</v>
+        <v>2529</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>ICT producing sector core indicators, annual</t>
+          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Information Economy</t>
+          <t>E-commerce</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Digital economy and technology &gt; Digital economy</t>
+          <t>Digital economy and technology &gt; E-commerce</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>ICT producing sector, employment, value added</t>
+          <t>e-commerce, digital ordering, digital trade, sales, business statistics</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T14:48:00</t>
+          <t>2026-05-21T08:57:00</t>
         </is>
       </c>
       <c r="J69" s="5" t="n">
@@ -6666,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>6495</v>
+        <v>906006</v>
       </c>
       <c r="N69" s="5" t="n">
         <v>0</v>
@@ -6713,48 +6705,48 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>US.IctGoodsShare</t>
+          <t>US.ECommerceInternational</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>2052</v>
+        <v>2530</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Share of ICT goods as percentage of total trade, annual</t>
+          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Information Economy</t>
+          <t>E-commerce</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>Digital economy and technology &gt; Digital economy</t>
+          <t>Digital economy and technology &gt; E-commerce</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Digital Economy, Information Economy, International Trade, ICT goods, Imports, Exports</t>
+          <t>e-commerce, digital trade, digital ordering, sales, turnover, business statistics</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>2025-12-01T13:06:00</t>
+          <t>2026-05-21T08:57:00</t>
         </is>
       </c>
       <c r="J70" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>110565343</v>
+        <v>139183</v>
       </c>
       <c r="N70" s="5" t="n">
         <v>0</v>
@@ -6763,7 +6755,7 @@
       <c r="P70" s="4" t="inlineStr"/>
       <c r="Q70" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R70" s="4" t="inlineStr"/>
@@ -6801,35 +6793,35 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceTotal</t>
+          <t>US.UCPI_A</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>2332</v>
+        <v>2274</v>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
+          <t>Commodity prices: UNCTAD Commodity Price Index - Annual</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>E-commerce</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Digital economy and technology &gt; E-commerce</t>
+          <t>Economy, investment and finance &gt; Commodity prices</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>e-commerce, digital ordering, digital trade, sales, business statistics</t>
+          <t>commodity, price, index</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T12:39:00</t>
+          <t>2026-02-10T12:49:00</t>
         </is>
       </c>
       <c r="J71" s="5" t="n">
@@ -6842,7 +6834,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>906006</v>
+        <v>4615</v>
       </c>
       <c r="N71" s="5" t="n">
         <v>0</v>
@@ -6889,35 +6881,35 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceInternational</t>
+          <t>US.UCPI_M</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>2333</v>
+        <v>2511</v>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
+          <t>Commodity prices: UNCTAD Commodity Price Index - Monthly</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>E-commerce</t>
+          <t>Commodities prices</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>Digital economy and technology &gt; E-commerce</t>
+          <t>Economy, investment and finance &gt; Commodity prices</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>e-commerce, digital trade, digital ordering, sales, turnover, business statistics</t>
+          <t>commodity, price, index</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T12:39:00</t>
+          <t>2026-07-17T13:17:00</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
@@ -6930,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>139183</v>
+        <v>66643</v>
       </c>
       <c r="N72" s="5" t="n">
         <v>0</v>
@@ -6977,15 +6969,15 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>US.UCPI_A</t>
+          <t>US.CommodityPrice_A</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>2274</v>
+        <v>1663</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Commodity prices: UNCTAD Commodity Price Index - Annual</t>
+          <t>DISCONTINUED - Commodity prices, 1995-2024, annual</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -7000,12 +6992,12 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>commodity, price, index</t>
+          <t>commodities, price</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10T12:49:00</t>
+          <t>2025-03-12T13:35:00</t>
         </is>
       </c>
       <c r="J73" s="5" t="n">
@@ -7018,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>4615</v>
+        <v>9629</v>
       </c>
       <c r="N73" s="5" t="n">
         <v>0</v>
@@ -7065,20 +7057,20 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>US.UCPI_M</t>
+          <t>US.CommodityPrice_M</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>2454</v>
+        <v>1899</v>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Commodity prices: UNCTAD Commodity Price Index - Monthly</t>
+          <t>DISCONTINUED - Commodity prices, January 1995 - June 2025, monthly</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Commodities prices</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -7088,12 +7080,12 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>commodity, price, index</t>
+          <t>commodity, price</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03T12:27:00</t>
+          <t>2025-08-11T14:32:00</t>
         </is>
       </c>
       <c r="J74" s="5" t="n">
@@ -7106,7 +7098,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>66552</v>
+        <v>84674</v>
       </c>
       <c r="N74" s="5" t="n">
         <v>0</v>
@@ -7153,15 +7145,15 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPrice_A</t>
+          <t>US.CommodityPriceIndices_A</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Commodity prices, 1995-2024, annual</t>
+          <t>DISCONTINUED - UNCTAD Commodity Price Index, 1995-2024, annual (2015=100)</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -7176,7 +7168,7 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>commodities, price</t>
+          <t>commodities, price, index</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -7194,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>9629</v>
+        <v>4522</v>
       </c>
       <c r="N75" s="5" t="n">
         <v>0</v>
@@ -7241,15 +7233,15 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPrice_M</t>
+          <t>US.CommodityPriceIndices_M</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Commodity prices, January 1995 - June 2025, monthly</t>
+          <t>DISCONTINUED - UNCTAD Commodity Price Index, January 1995 - June 2025, monthly (2015=100)</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -7264,7 +7256,7 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>commodity, price</t>
+          <t>commodity, price, index</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -7282,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>84674</v>
+        <v>66229</v>
       </c>
       <c r="N76" s="5" t="n">
         <v>0</v>
@@ -7329,35 +7321,35 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPriceIndices_A</t>
+          <t>US.GovExpenditures</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>1662</v>
+        <v>590</v>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - UNCTAD Commodity Price Index, 1995-2024, annual (2015=100)</t>
+          <t>Government expenditures</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Public Finance</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Economy, investment and finance &gt; Commodity prices</t>
+          <t>Economy, investment and finance &gt; Public finance</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>commodities, price, index</t>
+          <t>Government, expenditures, COFOG</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>2025-03-12T13:35:00</t>
+          <t>2023-07-18T16:51:00</t>
         </is>
       </c>
       <c r="J77" s="5" t="n">
@@ -7370,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>4522</v>
+        <v>248075</v>
       </c>
       <c r="N77" s="5" t="n">
         <v>0</v>
@@ -7417,48 +7409,48 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPriceIndices_M</t>
+          <t>US.BiotradeMerch</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>1900</v>
+        <v>2517</v>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - UNCTAD Commodity Price Index, January 1995 - June 2025, monthly (2015=100)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Merchandise biotrade</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Economy, investment and finance &gt; Commodity prices</t>
+          <t>Environment and related trade &gt; Trade in biodiversity-based products</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>commodity, price, index</t>
+          <t>Export, import, balance, value, merchandise, trade, biotrade, biodiversity, growth, rate</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>2025-08-11T14:32:00</t>
+          <t>2026-07-20T06:30:00</t>
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>66229</v>
+        <v>15552119339</v>
       </c>
       <c r="N78" s="5" t="n">
         <v>0</v>
@@ -7467,7 +7459,7 @@
       <c r="P78" s="4" t="inlineStr"/>
       <c r="Q78" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R78" s="4" t="inlineStr"/>
@@ -7505,35 +7497,35 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>US.GovExpenditures</t>
+          <t>US.BioTradeMerchMarketIndices</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>590</v>
+        <v>2124</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Government expenditures</t>
+          <t>Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Public Finance</t>
+          <t>Environment and related trade</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Economy, investment and finance &gt; Public finance</t>
+          <t>Environment and related trade &gt; Trade in biodiversity-based products</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Government, expenditures, COFOG</t>
+          <t>Export, import, merchandise, trade, market concentration, structural change, biotrade, biodiversity</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>2023-07-18T16:51:00</t>
+          <t>2025-11-28T16:02:00</t>
         </is>
       </c>
       <c r="J79" s="5" t="n">
@@ -7546,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>248075</v>
+        <v>623798</v>
       </c>
       <c r="N79" s="5" t="n">
         <v>0</v>
@@ -7593,48 +7585,48 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>US.BiotradeMerch</t>
+          <t>US.NonPlasticSubstsTradeByPartner</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>2123</v>
+        <v>1884</v>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Biotrade value and growth rates, annual (analytical)</t>
+          <t>Trade in non-plastic substitutes, annual (analytical)</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Merchandise biotrade</t>
+          <t>Environment and related trade</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in biodiversity-based products</t>
+          <t>Environment and related trade &gt; Trade in non-plastic substitutes</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Export, import, balance, value, merchandise, trade, biotrade, biodiversity, growth, rate</t>
+          <t>Plastics, trade, export, Non-plastic substitutes</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>2025-11-28T16:02:00</t>
+          <t>2025-08-04T06:56:00</t>
         </is>
       </c>
       <c r="J80" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>14582267024</v>
+        <v>511626169</v>
       </c>
       <c r="N80" s="5" t="n">
         <v>0</v>
@@ -7681,48 +7673,48 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchMarketIndices</t>
+          <t>US.OceanTrade</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>2124</v>
+        <v>2426</v>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Market concentration and structural change by product, annual (analytical)</t>
+          <t>Ocean goods: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in biodiversity-based products</t>
+          <t>Environment and related trade &gt; Trade in ocean goods and services</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Export, import, merchandise, trade, market concentration, structural change, biotrade, biodiversity</t>
+          <t>Oceans, international, trade, growth, sectors, maritime, sea</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>2025-11-28T16:02:00</t>
+          <t>2026-06-08T11:51:00</t>
         </is>
       </c>
       <c r="J81" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>623798</v>
+        <v>572108660</v>
       </c>
       <c r="N81" s="5" t="n">
         <v>0</v>
@@ -7731,7 +7723,7 @@
       <c r="P81" s="4" t="inlineStr"/>
       <c r="Q81" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R81" s="4" t="inlineStr"/>
@@ -7769,35 +7761,35 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>US.NonPlasticSubstsTradeByPartner</t>
+          <t>US.AssociatedPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>1884</v>
+        <v>1895</v>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Trade in non-plastic substitutes, annual (analytical)</t>
+          <t>Associated plastics trade by partner, annual (analytical)</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade</t>
+          <t>Plastics trade</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in non-plastic substitutes</t>
+          <t>Environment and related trade &gt; Trade in plastic-based products</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, export, Non-plastic substitutes</t>
+          <t>Associated plastics, trade, partner</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>2025-08-04T06:56:00</t>
+          <t>2025-08-04T07:52:00</t>
         </is>
       </c>
       <c r="J82" s="5" t="n">
@@ -7810,7 +7802,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>511626169</v>
+        <v>29490920</v>
       </c>
       <c r="N82" s="5" t="n">
         <v>0</v>
@@ -7857,35 +7849,35 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>US.OceanTrade</t>
+          <t>US.PlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>2426</v>
+        <v>1894</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Ocean goods: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Plastics trade by partner, annual (analytical)</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>Plastics trade</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in ocean goods and services</t>
+          <t>Environment and related trade &gt; Trade in plastic-based products</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Oceans, international, trade, growth, sectors, maritime, sea</t>
+          <t>Plastics, trade, export</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08T11:51:00</t>
+          <t>2025-08-04T07:52:00</t>
         </is>
       </c>
       <c r="J83" s="5" t="n">
@@ -7898,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>572108660</v>
+        <v>81455754</v>
       </c>
       <c r="N83" s="5" t="n">
         <v>0</v>
@@ -7945,15 +7937,15 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>US.AssociatedPlasticsTradebyPartner</t>
+          <t>US.HiddenPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Associated plastics trade by partner, annual (analytical)</t>
+          <t>Spotlight on selected plastic trade trends, by partner (analytical)</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -7968,7 +7960,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Associated plastics, trade, partner</t>
+          <t>Plastics, trade, partner, hs, product</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -7986,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>29490920</v>
+        <v>49942922</v>
       </c>
       <c r="N84" s="5" t="n">
         <v>0</v>
@@ -8033,48 +8025,48 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>US.PlasticsTradebyPartner</t>
+          <t>US.TradeFoodCatByProc</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>1894</v>
+        <v>1676</v>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Plastics trade by partner, annual (analytical)</t>
+          <t>Trade by food category, detailed by food processing (analytical)</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Plastics trade</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in plastic-based products</t>
+          <t>International trade &gt; Food trade by processing level</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, export</t>
+          <t>Food processing, food category, trade</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>2025-08-04T07:52:00</t>
+          <t>2025-03-20T12:39:00</t>
         </is>
       </c>
       <c r="J85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>81455754</v>
+        <v>2582634489</v>
       </c>
       <c r="N85" s="5" t="n">
         <v>0</v>
@@ -8121,48 +8113,48 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>US.HiddenPlasticsTradebyPartner</t>
+          <t>US.TradeFoodProcByCat</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1896</v>
+        <v>1677</v>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Spotlight on selected plastic trade trends, by partner (analytical)</t>
+          <t>Trade by food processing, detailed by food category (analytical)</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Plastics trade</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in plastic-based products</t>
+          <t>International trade &gt; Food trade by processing level</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, partner, hs, product</t>
+          <t>Food processing, food category, trade</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>2025-08-04T07:52:00</t>
+          <t>2025-03-20T12:39:00</t>
         </is>
       </c>
       <c r="J86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>49942922</v>
+        <v>2285091980</v>
       </c>
       <c r="N86" s="5" t="n">
         <v>0</v>
@@ -8209,48 +8201,48 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodCatByProc</t>
+          <t>US.CreativeGoodsValue</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>1676</v>
+        <v>2222</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Trade by food category, detailed by food processing (analytical)</t>
+          <t>Creative goods matrix, annual (analytical)</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>Creative economy</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Food trade by processing level</t>
+          <t>International trade &gt; Trade in creative goods and services</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Food processing, food category, trade</t>
+          <t>Creative goods, trade, exports, imports</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>2025-03-20T12:39:00</t>
+          <t>2026-04-02T15:01:00</t>
         </is>
       </c>
       <c r="J87" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K87" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>2582634489</v>
+        <v>335041684</v>
       </c>
       <c r="N87" s="5" t="n">
         <v>0</v>
@@ -8297,48 +8289,48 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodProcByCat</t>
+          <t>US.CreativeGoodsGR</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>1677</v>
+        <v>2220</v>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Trade by food processing, detailed by food category (analytical)</t>
+          <t>Creative goods matrix, growth rates, annual (analytical)</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>Creative economy</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Food trade by processing level</t>
+          <t>International trade &gt; Trade in creative goods and services</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Food processing, food category, trade</t>
+          <t>Creative goods, trade, exports, imports, growth rates</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>2025-03-20T12:39:00</t>
+          <t>2026-04-02T15:01:00</t>
         </is>
       </c>
       <c r="J88" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>2285091980</v>
+        <v>196623315</v>
       </c>
       <c r="N88" s="5" t="n">
         <v>0</v>
@@ -8385,15 +8377,15 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeGoodsValue</t>
+          <t>US.CreativeServ_Group_E</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>2222</v>
+        <v>2072</v>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Creative goods matrix, annual (analytical)</t>
+          <t>Creative services exports of selected groups of economies (analytical)</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -8408,25 +8400,25 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Creative goods, trade, exports, imports</t>
+          <t>Creative, services, trade, international, economy</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02T15:01:00</t>
+          <t>2026-04-02T15:05:00</t>
         </is>
       </c>
       <c r="J89" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>335041684</v>
+        <v>15132</v>
       </c>
       <c r="N89" s="5" t="n">
         <v>0</v>
@@ -8435,7 +8427,7 @@
       <c r="P89" s="4" t="inlineStr"/>
       <c r="Q89" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R89" s="4" t="inlineStr"/>
@@ -8473,35 +8465,35 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeGoodsGR</t>
+          <t>US.CriticalMinerals_TradeByPart</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>2220</v>
+        <v>2502</v>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Creative goods matrix, growth rates, annual (analytical)</t>
+          <t>Critical minerals: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Creative economy</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in creative goods and services</t>
+          <t>International trade &gt; Trade in critical minerals</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Creative goods, trade, exports, imports, growth rates</t>
+          <t>Trade, bilateral trade, exports, imports, merchandise trade, critical minerals, energy transition minerals, minerals, commodities, HS, products</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02T15:01:00</t>
+          <t>2026-07-14T09:51:00</t>
         </is>
       </c>
       <c r="J90" s="5" t="n">
@@ -8514,7 +8506,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>196623315</v>
+        <v>544826561</v>
       </c>
       <c r="N90" s="5" t="n">
         <v>0</v>
@@ -8561,48 +8553,48 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeServ_Group_E</t>
+          <t>US.GSTP_TradeMatrix</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>2072</v>
+        <v>2507</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Creative services exports of selected groups of economies (analytical)</t>
+          <t>GSTP: Merchandise trade matrix - Annual (analytical)</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Creative economy</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in creative goods and services</t>
+          <t>International trade &gt; Trade in merchandise</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Creative, services, trade, international, economy</t>
+          <t>International trade, structure, partner, economy, product, group, GSTP, Global System of Trade Preferences</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02T15:05:00</t>
+          <t>2026-07-15T13:43:00</t>
         </is>
       </c>
       <c r="J91" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>15132</v>
+        <v>371715547</v>
       </c>
       <c r="N91" s="5" t="n">
         <v>0</v>
@@ -8611,7 +8603,7 @@
       <c r="P91" s="4" t="inlineStr"/>
       <c r="Q91" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R91" s="4" t="inlineStr"/>
@@ -8649,35 +8641,35 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>US.CriticalMinerals_TradeByPart</t>
+          <t>US.IntraTrade</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>2502</v>
+        <v>2480</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Critical minerals: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Merchandise: Intra-trade and extra-trade of country groups by product, annual (analytical)</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in critical minerals</t>
+          <t>International trade &gt; Trade in merchandise</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Trade, bilateral trade, exports, imports, merchandise trade, critical minerals, energy transition minerals, minerals, commodities, HS, products</t>
+          <t>Intra-trade, extra-trade, value, share, group, region</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14T09:51:00</t>
+          <t>2026-07-08T10:38:00</t>
         </is>
       </c>
       <c r="J92" s="5" t="n">
@@ -8690,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>544826561</v>
+        <v>64011500</v>
       </c>
       <c r="N92" s="5" t="n">
         <v>0</v>
@@ -8737,15 +8729,15 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>US.GSTP_TradeMatrix</t>
+          <t>US.ConcentStructIndices</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>2507</v>
+        <v>2463</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>GSTP: Merchandise trade matrix - Annual (analytical)</t>
+          <t>Merchandise: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -8760,25 +8752,25 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>International trade, structure, partner, economy, product, group, GSTP, Global System of Trade Preferences</t>
+          <t>Indices, imports, exports, concentration, structural, trade</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T13:43:00</t>
+          <t>2026-07-09T11:36:00</t>
         </is>
       </c>
       <c r="J93" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>371715547</v>
+        <v>210324</v>
       </c>
       <c r="N93" s="5" t="n">
         <v>0</v>
@@ -8787,7 +8779,7 @@
       <c r="P93" s="4" t="inlineStr"/>
       <c r="Q93" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R93" s="4" t="inlineStr"/>
@@ -8825,15 +8817,15 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>US.IntraTrade</t>
+          <t>US.TradeMatrix</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Intra-trade and extra-trade of country groups by product, annual (analytical)</t>
+          <t>Merchandise: Trade matrix - Annual (analytical)</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -8848,7 +8840,7 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Intra-trade, extra-trade, value, share, group, region</t>
+          <t>International trade, structure, partner, economy, product, group</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -8857,16 +8849,16 @@
         </is>
       </c>
       <c r="J94" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>64011500</v>
+        <v>10989114010</v>
       </c>
       <c r="N94" s="5" t="n">
         <v>0</v>
@@ -8913,20 +8905,20 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>US.ConcentStructIndices</t>
+          <t>US.TradePriceIndices_Q</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>2463</v>
+        <v>2487</v>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Market concentration and structural change indices - Annual (analytical)</t>
+          <t>Merchandise: Trade price index – Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -8936,12 +8928,12 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Indices, imports, exports, concentration, structural, trade</t>
+          <t>Merchandises, Trade, Indices, Prices</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09T11:36:00</t>
+          <t>2026-07-10T15:13:00</t>
         </is>
       </c>
       <c r="J95" s="5" t="n">
@@ -8954,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>210324</v>
+        <v>114018</v>
       </c>
       <c r="N95" s="5" t="n">
         <v>0</v>
@@ -9001,15 +8993,15 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMatrix</t>
+          <t>US.TradeServCatByPartner</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>2482</v>
+        <v>2545</v>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade matrix - Annual (analytical)</t>
+          <t>Services: Bilateral trade by category - Annual</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -9019,30 +9011,30 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in merchandise</t>
+          <t>International trade &gt; Trade in services</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>International trade, structure, partner, economy, product, group</t>
+          <t>services, exports, imports, trade, bilateral, partner, transport, travel, sector, category</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08T10:38:00</t>
+          <t>2026-07-23T11:34:00</t>
         </is>
       </c>
       <c r="J96" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>10989114010</v>
+        <v>85648480</v>
       </c>
       <c r="N96" s="5" t="n">
         <v>0</v>
@@ -9089,48 +9081,48 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>US.TradePriceIndices_Q</t>
+          <t>US.TransportCosts</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>2487</v>
+        <v>1107</v>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade price index – Quarterly (analytical)</t>
+          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in merchandise</t>
+          <t>Maritime and other transport &gt; Global transport of merchandise trade</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Merchandises, Trade, Indices, Prices</t>
+          <t>international, trade, transport, cost, merchandise, product, destination, origin</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10T15:13:00</t>
+          <t>2024-05-22T09:00:00</t>
         </is>
       </c>
       <c r="J97" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>114018</v>
+        <v>34008028962</v>
       </c>
       <c r="N97" s="5" t="n">
         <v>0</v>
@@ -9139,7 +9131,7 @@
       <c r="P97" s="4" t="inlineStr"/>
       <c r="Q97" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R97" s="4" t="inlineStr"/>
@@ -9177,48 +9169,48 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatByPartner</t>
+          <t>US.PortCallsArrivals</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>1864</v>
+        <v>1065</v>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Services (BPM6): Exports and imports by service-category and by trade-partner, annual</t>
+          <t>Port call and performance statistics: number of port calls, annual (analytical)</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>Maritime transport</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in services</t>
+          <t>Maritime and other transport &gt; Port calls and performance</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>services, exports, imports, trade, bilateral, partner, transport, travel, sector, category</t>
+          <t>ships, port, maritime, transport, port calls, ports, time in port, vessels, services, container</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>2025-07-25T11:29:00</t>
+          <t>2024-03-28T16:25:00</t>
         </is>
       </c>
       <c r="J98" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>80172454</v>
+        <v>20304</v>
       </c>
       <c r="N98" s="5" t="n">
         <v>0</v>
@@ -9227,7 +9219,7 @@
       <c r="P98" s="4" t="inlineStr"/>
       <c r="Q98" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R98" s="4" t="inlineStr"/>
@@ -9265,48 +9257,48 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>US.TransportCosts</t>
+          <t>US.PortCallsArrivals_S</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>1107</v>
+        <v>1067</v>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
+          <t>Port call and performance statistics: number of port calls, semi-annual (analytical)</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>Maritime transport</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Global transport of merchandise trade</t>
+          <t>Maritime and other transport &gt; Port calls and performance</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>international, trade, transport, cost, merchandise, product, destination, origin</t>
+          <t>ships, port, maritime, transport, port calls, ports, time in port, vessels, services, container</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22T09:00:00</t>
+          <t>2024-03-28T16:25:00</t>
         </is>
       </c>
       <c r="J99" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>34008028962</v>
+        <v>38910</v>
       </c>
       <c r="N99" s="5" t="n">
         <v>0</v>
@@ -9315,7 +9307,7 @@
       <c r="P99" s="4" t="inlineStr"/>
       <c r="Q99" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R99" s="4" t="inlineStr"/>
@@ -9353,15 +9345,15 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>US.PortCallsArrivals</t>
+          <t>US.PortCalls</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: number of port calls, annual (analytical)</t>
+          <t>Port call and performance statistics: time spent in ports, vessel age and size, annual (analytical)</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -9381,7 +9373,7 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>2024-03-28T16:25:00</t>
+          <t>2024-03-28T16:47:00</t>
         </is>
       </c>
       <c r="J100" s="5" t="n">
@@ -9394,7 +9386,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>20304</v>
+        <v>19373</v>
       </c>
       <c r="N100" s="5" t="n">
         <v>0</v>
@@ -9441,15 +9433,15 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>US.PortCallsArrivals_S</t>
+          <t>US.PortCalls_S</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: number of port calls, semi-annual (analytical)</t>
+          <t>Port call and performance statistics: time spent in ports, vessel age and size, semi-annual (analytical)</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -9469,7 +9461,7 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>2024-03-28T16:25:00</t>
+          <t>2024-03-28T16:47:00</t>
         </is>
       </c>
       <c r="J101" s="5" t="n">
@@ -9482,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>38910</v>
+        <v>36462</v>
       </c>
       <c r="N101" s="5" t="n">
         <v>0</v>
@@ -9529,35 +9521,35 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>US.PortCalls</t>
+          <t>US.Gender_DomesticValueAdded</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>1064</v>
+        <v>1315</v>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: time spent in ports, vessel age and size, annual (analytical)</t>
+          <t>Domestic value added content in gross exports by sex and broad sector (analytical)</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Maritime transport</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Port calls and performance</t>
+          <t>Population and inclusiveness &gt; Gender and trade</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>ships, port, maritime, transport, port calls, ports, time in port, vessels, services, container</t>
+          <t>Trade, gender, gap, equality, employment, earnings, wages, domestic value added, export</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>2024-03-28T16:47:00</t>
+          <t>2024-10-10T12:39:00</t>
         </is>
       </c>
       <c r="J102" s="5" t="n">
@@ -9570,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>19373</v>
+        <v>97680</v>
       </c>
       <c r="N102" s="5" t="n">
         <v>0</v>
@@ -9617,35 +9609,35 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>US.PortCalls_S</t>
+          <t>US.InclusiveGrowth</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>1066</v>
+        <v>1631</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: time spent in ports, vessel age and size, semi-annual (analytical)</t>
+          <t>Inclusive Growth Index (IGI) (analytical)</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Maritime transport</t>
+          <t>Inclusive Growth</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Port calls and performance</t>
+          <t>Population and inclusiveness &gt; Inclusive growth</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>ships, port, maritime, transport, port calls, ports, time in port, vessels, services, container</t>
+          <t>Inclusive Growth Index, IGI, economic development, living conditions, social inclusion, environmental sustainability, equity</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>2024-03-28T16:47:00</t>
+          <t>2025-03-10T14:55:00</t>
         </is>
       </c>
       <c r="J103" s="5" t="n">
@@ -9658,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>36462</v>
+        <v>4221</v>
       </c>
       <c r="N103" s="5" t="n">
         <v>0</v>
@@ -9705,35 +9697,35 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_DomesticValueAdded</t>
+          <t>US.IFF_CrimesRelated</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>1315</v>
+        <v>2492</v>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Domestic value added content in gross exports by sex and broad sector (analytical)</t>
+          <t>Indicator 16.4.1: Crime-related illicit financial flows - Annual</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>SDG Indicators</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness &gt; Gender and trade</t>
+          <t>SDG Indicators &gt; Goal 16</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Trade, gender, gap, equality, employment, earnings, wages, domestic value added, export</t>
+          <t>IFF, crime-related, Drug, smuggling, trafficking, SDG 16.4.1, financial, inwards</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>2024-10-10T12:39:00</t>
+          <t>2026-06-09T09:17:00</t>
         </is>
       </c>
       <c r="J104" s="5" t="n">
@@ -9746,7 +9738,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>97680</v>
+        <v>2046</v>
       </c>
       <c r="N104" s="5" t="n">
         <v>0</v>
@@ -9793,35 +9785,35 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>US.InclusiveGrowth</t>
+          <t>US.IFF_TradeMisinvoicing</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>1631</v>
+        <v>2493</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth Index (IGI) (analytical)</t>
+          <t>Indicator 16.4.1: Trade misinvoicing illicit financial flows - Annual</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth</t>
+          <t>SDG Indicators</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness &gt; Inclusive growth</t>
+          <t>SDG Indicators &gt; Goal 16</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth Index, IGI, economic development, living conditions, social inclusion, environmental sustainability, equity</t>
+          <t>IFF, IFFs, Trade, misinvoicing, SDG, Tax, SDG</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>2025-03-10T14:55:00</t>
+          <t>2026-06-09T09:17:00</t>
         </is>
       </c>
       <c r="J105" s="5" t="n">
@@ -9834,7 +9826,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>4221</v>
+        <v>3342</v>
       </c>
       <c r="N105" s="5" t="n">
         <v>0</v>
@@ -9863,182 +9855,6 @@
         </is>
       </c>
       <c r="V105" s="4" t="inlineStr">
-        <is>
-          <t>https://unctadstat.unctad.org/datacentre/</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>UNCTADstat - UNCTAD</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela (Bolivarian Rep. of)</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>US.IFF_CrimesRelated</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="n">
-        <v>2492</v>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>Indicator 16.4.1: Crime-related illicit financial flows, IFFs - Annual</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>SDG Indicators</t>
-        </is>
-      </c>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t>SDG Indicators &gt; Goal 16</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>IFF, crime-related, Drug, smuggling, trafficking, SDG 16.4.1, financial, inwards</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09T09:17:00</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K106" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="5" t="n">
-        <v>2046</v>
-      </c>
-      <c r="N106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="4" t="inlineStr"/>
-      <c r="P106" s="4" t="inlineStr"/>
-      <c r="Q106" s="4" t="inlineStr">
-        <is>
-          <t>Sin valores descargados para Venezuela</t>
-        </is>
-      </c>
-      <c r="R106" s="4" t="inlineStr"/>
-      <c r="S106" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/unctad/csv/ove_unctadstat_venezuela_valores.csv.gz</t>
-        </is>
-      </c>
-      <c r="T106" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/unctad/catalog/unctad-catalog.json</t>
-        </is>
-      </c>
-      <c r="U106" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx</t>
-        </is>
-      </c>
-      <c r="V106" s="4" t="inlineStr">
-        <is>
-          <t>https://unctadstat.unctad.org/datacentre/</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>UNCTADstat - UNCTAD</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela (Bolivarian Rep. of)</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>US.IFF_TradeMisinvoicing</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="n">
-        <v>2493</v>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Indicator 16.4.1: Trade misinvoicing illicit financial flows, IFFs - Annual</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>SDG Indicators</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>SDG Indicators &gt; Goal 16</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>IFF, IFFs, Trade, misinvoicing, SDG, Tax, SDG</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09T09:17:00</t>
-        </is>
-      </c>
-      <c r="J107" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K107" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="5" t="n">
-        <v>3342</v>
-      </c>
-      <c r="N107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="4" t="inlineStr"/>
-      <c r="P107" s="4" t="inlineStr"/>
-      <c r="Q107" s="4" t="inlineStr">
-        <is>
-          <t>Sin valores descargados para Venezuela</t>
-        </is>
-      </c>
-      <c r="R107" s="4" t="inlineStr"/>
-      <c r="S107" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/unctad/csv/ove_unctadstat_venezuela_valores.csv.gz</t>
-        </is>
-      </c>
-      <c r="T107" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/unctad/catalog/unctad-catalog.json</t>
-        </is>
-      </c>
-      <c r="U107" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx</t>
-        </is>
-      </c>
-      <c r="V107" s="4" t="inlineStr">
         <is>
           <t>https://unctadstat.unctad.org/datacentre/</t>
         </is>
@@ -10056,7 +9872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10623,11 +10439,11 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 2005 to 2025</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>282378</v>
+        <v>304595</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
@@ -10635,10 +10451,10 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -10751,7 +10567,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Product concentration and diversification indices - Annual (analytical)</t>
+          <t>Merchandise: Standard product concentration and diversification indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -11022,26 +10838,26 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatQuarterlyAnnualized</t>
+          <t>US.TotAndComServicesQuarterly</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Services (BPM6), Preliminary annual estimates based on quarterly data: Exports and imports by main service-category</t>
+          <t>Services: Trade by main category - Quarterly</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>US_TradeServCatQuarterlyAnnualized</t>
+          <t>US_TotAndComServicesQuarterly</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2025</t>
+          <t>From 2005 to 2026</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>1379565</v>
+        <v>4997704</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
@@ -11049,14 +10865,14 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>480</v>
+        <v>1750</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>817</v>
+        <v>3610</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServCatQuarterlyAnnualized/US_TradeServCatQuarterlyAnnualized</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TotAndComServicesQuarterly/US_TotAndComServicesQuarterly</t>
         </is>
       </c>
     </row>
@@ -11068,17 +10884,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>US.TotAndComServicesQuarterly</t>
+          <t>US.TradeServCatTotal</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Services: Trade by main category - Quarterly</t>
+          <t>Services: Trade by category - Annual</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>US_TotAndComServicesQuarterly</t>
+          <t>US_TradeServCatTotal</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -11087,7 +10903,7 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>4712785</v>
+        <v>10102418</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
@@ -11095,14 +10911,14 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>1750</v>
+        <v>2949</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>3610</v>
+        <v>4793</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TotAndComServicesQuarterly/US_TotAndComServicesQuarterly</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServCatTotal/US_TradeServCatTotal</t>
         </is>
       </c>
     </row>
@@ -11114,41 +10930,41 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatTotal</t>
+          <t>US.TradeServCatByPartner</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Services (BPM6): Exports and imports by service category, trading partner world, annual</t>
+          <t>Services: Bilateral trade by category - Annual</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>US_TradeServCatTotal</t>
+          <t>US_TradeServCatByPartner</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 2005 to 2025</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>9743849</v>
+        <v>85648480</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>2823</v>
+        <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>4784</v>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServCatTotal/US_TradeServCatTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServCatByPartner/US_TradeServCatByPartner</t>
         </is>
       </c>
     </row>
@@ -11160,26 +10976,26 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatByPartner</t>
+          <t>US.CreativeGoodsValue</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Services (BPM6): Exports and imports by service-category and by trade-partner, annual</t>
+          <t>Creative goods matrix, annual (analytical)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>US_TradeServCatByPartner</t>
+          <t>US_CreativeGoodsValue</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 2002 to 2024</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>80172454</v>
+        <v>335041684</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -11194,7 +11010,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServCatByPartner/US_TradeServCatByPartner</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeGoodsValue/US_CreativeGoodsValue</t>
         </is>
       </c>
     </row>
@@ -11206,26 +11022,26 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeGoodsValue</t>
+          <t>US.CreativeGoodsGR</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Creative goods matrix, annual (analytical)</t>
+          <t>Creative goods matrix, growth rates, annual (analytical)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>US_CreativeGoodsValue</t>
+          <t>US_CreativeGoodsGR</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>From 2002 to 2024</t>
+          <t>The whole dataset</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>335041684</v>
+        <v>196623315</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
@@ -11240,7 +11056,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeGoodsValue/US_CreativeGoodsValue</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeGoodsGR/US_CreativeGoodsGR</t>
         </is>
       </c>
     </row>
@@ -11252,41 +11068,41 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeGoodsGR</t>
+          <t>US.CreativeServ_Indiv_Tot</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Creative goods matrix, growth rates, annual (analytical)</t>
+          <t>International trade in creative services: estimates for individual economies (analytical)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>US_CreativeGoodsGR</t>
+          <t>US_CreativeServ_Indiv_Tot</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>The whole dataset</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>196623315</v>
+        <v>62133</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeGoodsGR/US_CreativeGoodsGR</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeServ_Indiv_Tot/US_CreativeServ_Indiv_Tot</t>
         </is>
       </c>
     </row>
@@ -11298,17 +11114,17 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeServ_Indiv_Tot</t>
+          <t>US.CreativeServ_Group_E</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>International trade in creative services: estimates for individual economies (analytical)</t>
+          <t>Creative services exports of selected groups of economies (analytical)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>US_CreativeServ_Indiv_Tot</t>
+          <t>US_CreativeServ_Group_E</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -11317,7 +11133,7 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>62133</v>
+        <v>15132</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
@@ -11325,14 +11141,14 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeServ_Indiv_Tot/US_CreativeServ_Indiv_Tot</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeServ_Group_E/US_CreativeServ_Group_E</t>
         </is>
       </c>
     </row>
@@ -11344,30 +11160,30 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeServ_Group_E</t>
+          <t>US.CriticalMinerals_TradeByPart</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Creative services exports of selected groups of economies (analytical)</t>
+          <t>Critical minerals: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>US_CreativeServ_Group_E</t>
+          <t>US_CriticalMinerals_TradeByPart</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2002 to 2024</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>15132</v>
+        <v>544826561</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -11378,7 +11194,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeServ_Group_E/US_CreativeServ_Group_E</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CriticalMinerals_TradeByPart/US_CriticalMinerals_TradeByPart</t>
         </is>
       </c>
     </row>
@@ -11390,26 +11206,26 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>US.CriticalMinerals_TradeByPart</t>
+          <t>US.TradeFoodCatByProc</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Critical minerals: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Trade by food category, detailed by food processing (analytical)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>US_CriticalMinerals_TradeByPart</t>
+          <t>US_TradeFoodCatByProc_19952009</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>From 2002 to 2024</t>
+          <t>From 1995 to 2009</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>544826561</v>
+        <v>1242404356</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
@@ -11424,7 +11240,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CriticalMinerals_TradeByPart/US_CriticalMinerals_TradeByPart</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodCatByProc/US_TradeFoodCatByProc_19952009</t>
         </is>
       </c>
     </row>
@@ -11446,16 +11262,16 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodCatByProc_19952009</t>
+          <t>US_TradeFoodCatByProc_20102023</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2009</t>
+          <t>From 2010 to 2023</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1242404356</v>
+        <v>1340230133</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
@@ -11470,7 +11286,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodCatByProc/US_TradeFoodCatByProc_19952009</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodCatByProc/US_TradeFoodCatByProc_20102023</t>
         </is>
       </c>
     </row>
@@ -11482,41 +11298,41 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodCatByProc</t>
+          <t>US.TradeFoodProcCat_Cat_RCA</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Trade by food category, detailed by food processing (analytical)</t>
+          <t>Trade by food category, detailed by food processing, RCA (analytical)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodCatByProc_20102023</t>
+          <t>US_TradeFoodProcCat_Cat_RCA</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2023</t>
+          <t>From 1995 to 2023</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>1340230133</v>
+        <v>3467211</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0</v>
+        <v>2589</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0</v>
+        <v>2589</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodCatByProc/US_TradeFoodCatByProc_20102023</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcCat_Cat_RCA/US_TradeFoodProcCat_Cat_RCA</t>
         </is>
       </c>
     </row>
@@ -11528,41 +11344,41 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodProcCat_Cat_RCA</t>
+          <t>US.TradeFoodProcByCat</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Trade by food category, detailed by food processing, RCA (analytical)</t>
+          <t>Trade by food processing, detailed by food category (analytical)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodProcCat_Cat_RCA</t>
+          <t>US_TradeFoodProcByCat_19952009</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2023</t>
+          <t>From 1995 to 2009</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>3467211</v>
+        <v>1099284426</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>2589</v>
+        <v>0</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>2589</v>
+        <v>0</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcCat_Cat_RCA/US_TradeFoodProcCat_Cat_RCA</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcByCat/US_TradeFoodProcByCat_19952009</t>
         </is>
       </c>
     </row>
@@ -11584,16 +11400,16 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodProcByCat_19952009</t>
+          <t>US_TradeFoodProcByCat_20102023</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2009</t>
+          <t>From 2010 to 2023</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>1099284426</v>
+        <v>1185807554</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
@@ -11608,7 +11424,7 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcByCat/US_TradeFoodProcByCat_19952009</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcByCat/US_TradeFoodProcByCat_20102023</t>
         </is>
       </c>
     </row>
@@ -11620,41 +11436,41 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodProcByCat</t>
+          <t>US.TradeFoodProcCat_Proc_RCA</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Trade by food processing, detailed by food category (analytical)</t>
+          <t>Trade by food processing, detailed by food category, RCA (analytical)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodProcByCat_20102023</t>
+          <t>US_TradeFoodProcCat_Proc_RCA</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2023</t>
+          <t>From 1995 to 2023</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>1185807554</v>
+        <v>3796561</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0</v>
+        <v>2845</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>0</v>
+        <v>2845</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcByCat/US_TradeFoodProcByCat_20102023</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcCat_Proc_RCA/US_TradeFoodProcCat_Proc_RCA</t>
         </is>
       </c>
     </row>
@@ -11666,26 +11482,26 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodProcCat_Proc_RCA</t>
+          <t>US.GDPTotal</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Trade by food processing, detailed by food category, RCA (analytical)</t>
+          <t>Gross domestic product: Total and per capita - Annual</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodProcCat_Proc_RCA</t>
+          <t>US_GDPTotal</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2023</t>
+          <t>From 1970 to 2025</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>3796561</v>
+        <v>425702</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
@@ -11693,14 +11509,14 @@
         </is>
       </c>
       <c r="H40" s="5" t="n">
-        <v>2845</v>
+        <v>56</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>2845</v>
+        <v>332</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcCat_Proc_RCA/US_TradeFoodProcCat_Proc_RCA</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GDPTotal/US_GDPTotal</t>
         </is>
       </c>
     </row>
@@ -11712,26 +11528,26 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>US.GDPTotal</t>
+          <t>US.GDPComponent</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product: Total and per capita - Annual</t>
+          <t>Gross domestic product: GDP by type of expenditure, VA by kind of economic activity, total and shares, annual</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>US_GDPTotal</t>
+          <t>US_GDPComponent</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>From 1970 to 2025</t>
+          <t>From 1970 to 2024</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>425702</v>
+        <v>4425120</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -11739,14 +11555,14 @@
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>56</v>
+        <v>1045</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>332</v>
+        <v>3135</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GDPTotal/US_GDPTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GDPComponent/US_GDPComponent</t>
         </is>
       </c>
     </row>
@@ -11758,26 +11574,26 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>US.GDPComponent</t>
+          <t>US.GNI</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product: GDP by type of expenditure, VA by kind of economic activity, total and shares, annual</t>
+          <t>DISCONTINUED - Nominal GNI, total and per capita, annual</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>US_GDPComponent</t>
+          <t>US_GNI</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>From 1970 to 2024</t>
+          <t>The whole period</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>4425120</v>
+        <v>145178</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
@@ -11785,14 +11601,14 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>1045</v>
+        <v>51</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>3135</v>
+        <v>102</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GDPComponent/US_GDPComponent</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GNI/US_GNI</t>
         </is>
       </c>
     </row>
@@ -11804,26 +11620,26 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>US.GNI</t>
+          <t>US.GoodsAndServicesBpm6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Nominal GNI, total and per capita, annual</t>
+          <t>Goods and services (BPM6): Exports and imports of goods and services, annual</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>US_GNI</t>
+          <t>US_GoodsAndServicesBpm6</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>The whole period</t>
+          <t>From 2005 to 2024</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>145178</v>
+        <v>362860</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
@@ -11831,14 +11647,14 @@
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GNI/US_GNI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServicesBpm6/US_GoodsAndServicesBpm6</t>
         </is>
       </c>
     </row>
@@ -11850,17 +11666,17 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>US.GoodsAndServicesBpm6</t>
+          <t>US.GoodsAndServBalanceBpm6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Goods and services (BPM6): Exports and imports of goods and services, annual</t>
+          <t>Goods and services (BPM6): Trade balance indicators, annual</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>US_GoodsAndServicesBpm6</t>
+          <t>US_GoodsAndServBalanceBpm6</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -11869,7 +11685,7 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>362860</v>
+        <v>305732</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
@@ -11877,14 +11693,14 @@
         </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServicesBpm6/US_GoodsAndServicesBpm6</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServBalanceBpm6/US_GoodsAndServBalanceBpm6</t>
         </is>
       </c>
     </row>
@@ -11896,17 +11712,17 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>US.GoodsAndServBalanceBpm6</t>
+          <t>US.GoodsAndServTradeOpennessBpm6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Goods and services (BPM6): Trade balance indicators, annual</t>
+          <t>Goods and services (BPM6): Trade openness indicators, annual</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>US_GoodsAndServBalanceBpm6</t>
+          <t>US_GoodsAndServTradeOpennessBpm6</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -11915,7 +11731,7 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>305732</v>
+        <v>859488</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
@@ -11923,14 +11739,14 @@
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServBalanceBpm6/US_GoodsAndServBalanceBpm6</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServTradeOpennessBpm6/US_GoodsAndServTradeOpennessBpm6</t>
         </is>
       </c>
     </row>
@@ -11942,26 +11758,26 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>US.GoodsAndServTradeOpennessBpm6</t>
+          <t>US.CurrAccBalance</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Goods and services (BPM6): Trade openness indicators, annual</t>
+          <t>Balance of payments, Current account balance, annual</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>US_GoodsAndServTradeOpennessBpm6</t>
+          <t>US_CurrAccBalance</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 1980 to 2024</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>859488</v>
+        <v>120600</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
@@ -11969,14 +11785,14 @@
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>360</v>
+        <v>74</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServTradeOpennessBpm6/US_GoodsAndServTradeOpennessBpm6</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CurrAccBalance/US_CurrAccBalance</t>
         </is>
       </c>
     </row>
@@ -11988,26 +11804,26 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>US.CurrAccBalance</t>
+          <t>US.FdiFlowsStock</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Balance of payments, Current account balance, annual</t>
+          <t>Foreign direct investment: Inward and outward flows and stock, annual</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>US_CurrAccBalance</t>
+          <t>US_FdiFlowsStock</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>From 1980 to 2024</t>
+          <t>From 1990 to 2024</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>120600</v>
+        <v>370935</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
@@ -12015,14 +11831,14 @@
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>74</v>
+        <v>280</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CurrAccBalance/US_CurrAccBalance</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FdiFlowsStock/US_FdiFlowsStock</t>
         </is>
       </c>
     </row>
@@ -12034,26 +11850,26 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>US.FdiFlowsStock</t>
+          <t>US.Remittances</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Foreign direct investment: Inward and outward flows and stock, annual</t>
+          <t>Personal remittances: receipts and payments, annual</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>US_FdiFlowsStock</t>
+          <t>US_Remittances</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>From 1990 to 2024</t>
+          <t>From 2000 to 2024</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>370935</v>
+        <v>69641</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
@@ -12061,14 +11877,14 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FdiFlowsStock/US_FdiFlowsStock</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Remittances/US_Remittances</t>
         </is>
       </c>
     </row>
@@ -12080,17 +11896,17 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>US.Remittances</t>
+          <t>US.PCI</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Personal remittances: receipts and payments, annual</t>
+          <t>Productive capacities index, annual, 2000-2024 (analytical)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>US_Remittances</t>
+          <t>US_PCI</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -12099,7 +11915,7 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>69641</v>
+        <v>292674</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
@@ -12107,14 +11923,14 @@
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Remittances/US_Remittances</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PCI/US_PCI</t>
         </is>
       </c>
     </row>
@@ -12126,26 +11942,26 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>US.PCI</t>
+          <t>US.Cpi_A</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Productive capacities index, annual, 2000-2024 (analytical)</t>
+          <t>Consumer price indices, annual (analytical)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>US_PCI</t>
+          <t>US_Cpi_A</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>The whole period</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>292674</v>
+        <v>102323</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
@@ -12153,14 +11969,14 @@
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>225</v>
+        <v>43</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PCI/US_PCI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Cpi_A/US_Cpi_A</t>
         </is>
       </c>
     </row>
@@ -12172,26 +11988,26 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>US.Cpi_A</t>
+          <t>US.ExchangeRateCrosstab</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Consumer price indices, annual (analytical)</t>
+          <t>Exchange rates: Currency cross rates - Annual</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>US_Cpi_A</t>
+          <t>US_ExchangeRateCrosstab</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>The whole period</t>
+          <t>From 1970 to 2025</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>102323</v>
+        <v>18056762</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
@@ -12199,14 +12015,14 @@
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>43</v>
+        <v>26488</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>85</v>
+        <v>23205</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Cpi_A/US_Cpi_A</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ExchangeRateCrosstab/US_ExchangeRateCrosstab</t>
         </is>
       </c>
     </row>
@@ -12218,26 +12034,26 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>US.ExchangeRateCrosstab</t>
+          <t>US.UCPI_A</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Exchange rates: Currency cross rates - Annual</t>
+          <t>Commodity prices: UNCTAD Commodity Price Index - Annual</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>US_ExchangeRateCrosstab</t>
+          <t>US_UCPI_A</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>From 1970 to 2025</t>
+          <t>From 1995 to 2025</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>18056762</v>
+        <v>4615</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
@@ -12245,14 +12061,14 @@
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>26488</v>
+        <v>0</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>23205</v>
+        <v>0</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ExchangeRateCrosstab/US_ExchangeRateCrosstab</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.UCPI_A/US_UCPI_A</t>
         </is>
       </c>
     </row>
@@ -12264,26 +12080,26 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>US.UCPI_A</t>
+          <t>US.UCPI_M</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Commodity prices: UNCTAD Commodity Price Index - Annual</t>
+          <t>Commodity prices: UNCTAD Commodity Price Index - Monthly</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>US_UCPI_A</t>
+          <t>US_UCPI_M</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2025</t>
+          <t>From 1995 to 2026</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>4615</v>
+        <v>66643</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
@@ -12298,7 +12114,7 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.UCPI_A/US_UCPI_A</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.UCPI_M/US_UCPI_M</t>
         </is>
       </c>
     </row>
@@ -12310,26 +12126,26 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>US.UCPI_M</t>
+          <t>US.CommodityPriceIndices_A</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Commodity prices: UNCTAD Commodity Price Index - Monthly</t>
+          <t>DISCONTINUED - UNCTAD Commodity Price Index, 1995-2024, annual (2015=100)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>US_UCPI_M</t>
+          <t>US_CommodityPriceIndices_A</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2026</t>
+          <t>From 1995 to 2025</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>66552</v>
+        <v>4522</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
@@ -12344,7 +12160,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.UCPI_M/US_UCPI_M</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPriceIndices_A/US_CommodityPriceIndices_A</t>
         </is>
       </c>
     </row>
@@ -12356,17 +12172,17 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPriceIndices_A</t>
+          <t>US.CommodityPriceIndices_M</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - UNCTAD Commodity Price Index, 1995-2024, annual (2015=100)</t>
+          <t>DISCONTINUED - UNCTAD Commodity Price Index, January 1995 - June 2025, monthly (2015=100)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>US_CommodityPriceIndices_A</t>
+          <t>US_CommodityPriceIndices_M</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -12375,7 +12191,7 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>4522</v>
+        <v>66229</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
@@ -12390,7 +12206,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPriceIndices_A/US_CommodityPriceIndices_A</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPriceIndices_M/US_CommodityPriceIndices_M</t>
         </is>
       </c>
     </row>
@@ -12402,17 +12218,17 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPriceIndices_M</t>
+          <t>US.CommodityPrice_A</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - UNCTAD Commodity Price Index, January 1995 - June 2025, monthly (2015=100)</t>
+          <t>DISCONTINUED - Commodity prices, 1995-2024, annual</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>US_CommodityPriceIndices_M</t>
+          <t>US_CommodityPrice_A</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -12421,7 +12237,7 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>66229</v>
+        <v>9629</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
@@ -12436,7 +12252,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPriceIndices_M/US_CommodityPriceIndices_M</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPrice_A/US_CommodityPrice_A</t>
         </is>
       </c>
     </row>
@@ -12448,17 +12264,17 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPrice_A</t>
+          <t>US.CommodityPrice_M</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Commodity prices, 1995-2024, annual</t>
+          <t>DISCONTINUED - Commodity prices, January 1995 - June 2025, monthly</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>US_CommodityPrice_A</t>
+          <t>US_CommodityPrice_M</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -12467,7 +12283,7 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>9629</v>
+        <v>84674</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
@@ -12482,7 +12298,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPrice_A/US_CommodityPrice_A</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPrice_M/US_CommodityPrice_M</t>
         </is>
       </c>
     </row>
@@ -12494,26 +12310,26 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPrice_M</t>
+          <t>US.GovExpenditures</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Commodity prices, January 1995 - June 2025, monthly</t>
+          <t>Government expenditures</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>US_CommodityPrice_M</t>
+          <t>US_GovExpenditures</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2025</t>
+          <t>The whole period</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>84674</v>
+        <v>248075</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
@@ -12528,7 +12344,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPrice_M/US_CommodityPrice_M</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GovExpenditures/US_GovExpenditures</t>
         </is>
       </c>
     </row>
@@ -12540,26 +12356,26 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>US.GovExpenditures</t>
+          <t>US.MerchantFleet</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Government expenditures</t>
+          <t>Merchant fleet: World fleet by flag of registration and ship type - Core indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>US_GovExpenditures</t>
+          <t>US_MerchantFleet</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>The whole period</t>
+          <t>From 1980 to 2026</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>248075</v>
+        <v>938045</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
@@ -12567,14 +12383,14 @@
         </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GovExpenditures/US_GovExpenditures</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.MerchantFleet/US_MerchantFleet</t>
         </is>
       </c>
     </row>
@@ -12586,26 +12402,26 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>US.MerchantFleet</t>
+          <t>US.FleetBeneficialOwners</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by flag of registration and ship type - Core indicators - Annual (analytical)</t>
+          <t>Merchant fleet: World fleet by beneficial ownership - Core indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>US_MerchantFleet</t>
+          <t>US_FleetBeneficialOwners</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>From 1980 to 2026</t>
+          <t>From 2014 to 2026</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>938045</v>
+        <v>412428</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
@@ -12613,14 +12429,14 @@
         </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>1102</v>
+        <v>897</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.MerchantFleet/US_MerchantFleet</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FleetBeneficialOwners/US_FleetBeneficialOwners</t>
         </is>
       </c>
     </row>
@@ -12632,26 +12448,26 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>US.FleetBeneficialOwners</t>
+          <t>US.VesselValueByRegistration</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by beneficial ownership - Core indicators - Annual (analytical)</t>
+          <t>Merchant fleet: World fleet by flag of registration - Annual (analytical)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>US_FleetBeneficialOwners</t>
+          <t>US_VesselValueByRegistration</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>From 2014 to 2026</t>
+          <t>From 2019 to 2026</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>412428</v>
+        <v>9782</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
@@ -12659,14 +12475,14 @@
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>897</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FleetBeneficialOwners/US_FleetBeneficialOwners</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.VesselValueByRegistration/US_VesselValueByRegistration</t>
         </is>
       </c>
     </row>
@@ -12678,17 +12494,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>US.VesselValueByRegistration</t>
+          <t>US.VesselValueByOwnership</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by flag of registration - Annual (analytical)</t>
+          <t>Merchant fleet: World fleet by beneficial ownership - Annual (analytical)</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>US_VesselValueByRegistration</t>
+          <t>US_VesselValueByOwnership</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -12697,7 +12513,7 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>9782</v>
+        <v>9851</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
@@ -12712,7 +12528,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.VesselValueByRegistration/US_VesselValueByRegistration</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.VesselValueByOwnership/US_VesselValueByOwnership</t>
         </is>
       </c>
     </row>
@@ -12724,26 +12540,26 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>US.VesselValueByOwnership</t>
+          <t>US.ShipBuilding</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by beneficial ownership - Annual (analytical)</t>
+          <t>Ship building: Merchant fleet built - Annual (analytical)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>US_VesselValueByOwnership</t>
+          <t>US_ShipBuilding</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>From 2019 to 2026</t>
+          <t>From 2014 to 2025</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>9851</v>
+        <v>11070</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
@@ -12751,14 +12567,14 @@
         </is>
       </c>
       <c r="H63" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.VesselValueByOwnership/US_VesselValueByOwnership</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ShipBuilding/US_ShipBuilding</t>
         </is>
       </c>
     </row>
@@ -12770,17 +12586,17 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>US.ShipBuilding</t>
+          <t>US.ShipScrapping</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Ship building: Merchant fleet built - Annual (analytical)</t>
+          <t>Ship recycling: Merchant fleet recycled - Annual (analytical)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>US_ShipBuilding</t>
+          <t>US_ShipScrapping</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -12789,7 +12605,7 @@
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>11070</v>
+        <v>8908</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
@@ -12797,14 +12613,14 @@
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ShipBuilding/US_ShipBuilding</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ShipScrapping/US_ShipScrapping</t>
         </is>
       </c>
     </row>
@@ -12816,26 +12632,26 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>US.ShipScrapping</t>
+          <t>US.SeaborneTrade</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Ship recycling: Merchant fleet recycled - Annual (analytical)</t>
+          <t>World seaborne trade by type of cargo, annual (analytical)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>US_ShipScrapping</t>
+          <t>US_SeaborneTrade</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>From 2014 to 2025</t>
+          <t>From 2000 to 2024</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>8908</v>
+        <v>462110</v>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
@@ -12843,14 +12659,14 @@
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>5</v>
+        <v>225</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>10</v>
+        <v>225</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ShipScrapping/US_ShipScrapping</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SeaborneTrade/US_SeaborneTrade</t>
         </is>
       </c>
     </row>
@@ -12862,26 +12678,26 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>US.SeaborneTrade</t>
+          <t>US.ContPortThroughput</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>World seaborne trade by type of cargo, annual (analytical)</t>
+          <t>Container port throughput, annual (analytical)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>US_SeaborneTrade</t>
+          <t>US_ContPortThroughput</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>462110</v>
+        <v>16188</v>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
@@ -12889,14 +12705,14 @@
         </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>225</v>
+        <v>15</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>225</v>
+        <v>12</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SeaborneTrade/US_SeaborneTrade</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ContPortThroughput/US_ContPortThroughput</t>
         </is>
       </c>
     </row>
@@ -12908,26 +12724,26 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>US.ContPortThroughput</t>
+          <t>US.PortCalls</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Container port throughput, annual (analytical)</t>
+          <t>Port call and performance statistics: time spent in ports, vessel age and size, annual (analytical)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>US_ContPortThroughput</t>
+          <t>US_PortCalls</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2018 to 2023</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>16188</v>
+        <v>19373</v>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
@@ -12935,14 +12751,14 @@
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ContPortThroughput/US_ContPortThroughput</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCalls/US_PortCalls</t>
         </is>
       </c>
     </row>
@@ -12954,17 +12770,17 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>US.PortCalls</t>
+          <t>US.PortCalls_S</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: time spent in ports, vessel age and size, annual (analytical)</t>
+          <t>Port call and performance statistics: time spent in ports, vessel age and size, semi-annual (analytical)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>US_PortCalls</t>
+          <t>US_PortCalls_S</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -12973,7 +12789,7 @@
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>19373</v>
+        <v>36462</v>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
@@ -12988,7 +12804,7 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCalls/US_PortCalls</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCalls_S/US_PortCalls_S</t>
         </is>
       </c>
     </row>
@@ -13000,17 +12816,17 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>US.PortCalls_S</t>
+          <t>US.PortCallsArrivals</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: time spent in ports, vessel age and size, semi-annual (analytical)</t>
+          <t>Port call and performance statistics: number of port calls, annual (analytical)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>US_PortCalls_S</t>
+          <t>US_PortCallsArrivals</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -13019,7 +12835,7 @@
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>36462</v>
+        <v>20304</v>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
@@ -13034,7 +12850,7 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCalls_S/US_PortCalls_S</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCallsArrivals/US_PortCallsArrivals</t>
         </is>
       </c>
     </row>
@@ -13046,17 +12862,17 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>US.PortCallsArrivals</t>
+          <t>US.PortCallsArrivals_S</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: number of port calls, annual (analytical)</t>
+          <t>Port call and performance statistics: number of port calls, semi-annual (analytical)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>US_PortCallsArrivals</t>
+          <t>US_PortCallsArrivals_S</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -13065,7 +12881,7 @@
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>20304</v>
+        <v>38910</v>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
@@ -13080,7 +12896,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCallsArrivals/US_PortCallsArrivals</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCallsArrivals_S/US_PortCallsArrivals_S</t>
         </is>
       </c>
     </row>
@@ -13092,26 +12908,26 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>US.PortCallsArrivals_S</t>
+          <t>US.LSCI_M</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: number of port calls, semi-annual (analytical)</t>
+          <t>Liner shipping: Connectivity index - Monthly (analytical)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>US_PortCallsArrivals_S</t>
+          <t>US_LSCI_M</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>From 2018 to 2023</t>
+          <t>From 2006 to 2026</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>38910</v>
+        <v>209318</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
@@ -13119,14 +12935,14 @@
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCallsArrivals_S/US_PortCallsArrivals_S</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSCI_M/US_LSCI_M</t>
         </is>
       </c>
     </row>
@@ -13138,17 +12954,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>US.LSCI_M</t>
+          <t>US.LSCI</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Connectivity index - Monthly (analytical)</t>
+          <t>Liner shipping: Connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>US_LSCI_M</t>
+          <t>US_LSCI</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -13157,7 +12973,7 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>209318</v>
+        <v>203416</v>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
@@ -13165,14 +12981,14 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>249</v>
+        <v>323</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSCI_M/US_LSCI_M</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSCI/US_LSCI</t>
         </is>
       </c>
     </row>
@@ -13184,17 +13000,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>US.LSCI</t>
+          <t>US.LSBCI</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Connectivity index - Quarterly (analytical)</t>
+          <t>Liner shipping: Bilateral connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>US_LSCI</t>
+          <t>US_LSBCI</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -13203,7 +13019,7 @@
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>203416</v>
+        <v>3456483</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
@@ -13211,14 +13027,14 @@
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>82</v>
+        <v>7565</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>323</v>
+        <v>7398</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSCI/US_LSCI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSBCI/US_LSBCI</t>
         </is>
       </c>
     </row>
@@ -13230,17 +13046,17 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>US.LSBCI</t>
+          <t>US.PLSCI</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Bilateral connectivity index - Quarterly (analytical)</t>
+          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>US_LSBCI</t>
+          <t>US_PLSCI</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -13249,7 +13065,7 @@
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>3456483</v>
+        <v>355602</v>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
@@ -13257,14 +13073,14 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>7565</v>
+        <v>716</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>7398</v>
+        <v>716</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSBCI/US_LSBCI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PLSCI/US_PLSCI</t>
         </is>
       </c>
     </row>
@@ -13276,26 +13092,26 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>US.PLSCI</t>
+          <t>US.Seafarers</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
+          <t>Seafarer supply, quinquennial, 2015 and 2021 (analytical)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>US_PLSCI</t>
+          <t>US_Seafarers</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>From 2006 to 2026</t>
+          <t>From 2015 to 2021</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>355602</v>
+        <v>11519</v>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
@@ -13303,14 +13119,14 @@
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>716</v>
+        <v>6</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>716</v>
+        <v>12</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PLSCI/US_PLSCI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Seafarers/US_Seafarers</t>
         </is>
       </c>
     </row>
@@ -13322,41 +13138,41 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>US.Seafarers</t>
+          <t>US.TransportCosts</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Seafarer supply, quinquennial, 2015 and 2021 (analytical)</t>
+          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>US_Seafarers</t>
+          <t>US_TransportCosts_20162016</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>From 2015 to 2021</t>
+          <t>From 2016 to 2016</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>11519</v>
+        <v>5808744649</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Seafarers/US_Seafarers</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20162016</t>
         </is>
       </c>
     </row>
@@ -13378,16 +13194,16 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20162016</t>
+          <t>US_TransportCosts_20172017</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>From 2016 to 2016</t>
+          <t>From 2017 to 2017</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>5808744649</v>
+        <v>5505087830</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
@@ -13402,7 +13218,7 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20162016</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20172017</t>
         </is>
       </c>
     </row>
@@ -13424,16 +13240,16 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20172017</t>
+          <t>US_TransportCosts_20182018</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>From 2017 to 2017</t>
+          <t>From 2018 to 2018</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>5505087830</v>
+        <v>5587492705</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -13448,7 +13264,7 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20172017</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20182018</t>
         </is>
       </c>
     </row>
@@ -13470,16 +13286,16 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20182018</t>
+          <t>US_TransportCosts_20192019</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>From 2018 to 2018</t>
+          <t>From 2019 to 2019</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>5587492705</v>
+        <v>5666291146</v>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
@@ -13494,7 +13310,7 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20182018</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20192019</t>
         </is>
       </c>
     </row>
@@ -13516,16 +13332,16 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20192019</t>
+          <t>US_TransportCosts_20202020</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>From 2019 to 2019</t>
+          <t>From 2020 to 2020</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>5666291146</v>
+        <v>5621158940</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -13540,7 +13356,7 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20192019</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20202020</t>
         </is>
       </c>
     </row>
@@ -13562,16 +13378,16 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20202020</t>
+          <t>US_TransportCosts_20212021</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>From 2020 to 2020</t>
+          <t>From 2021 to 2021</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>5621158940</v>
+        <v>5819253692</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
@@ -13586,7 +13402,7 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20202020</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20212021</t>
         </is>
       </c>
     </row>
@@ -13598,26 +13414,26 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>US.TransportCosts</t>
+          <t>US.BiotradeMerch</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20212021</t>
+          <t>US_BiotradeMerch_20102011</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>From 2021 to 2021</t>
+          <t>From 2010 to 2011</t>
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>5819253692</v>
+        <v>2156853807</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
@@ -13632,7 +13448,7 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20212021</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20102011</t>
         </is>
       </c>
     </row>
@@ -13649,21 +13465,21 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Biotrade value and growth rates, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20102011</t>
+          <t>US_BiotradeMerch_20122013</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2011</t>
+          <t>From 2012 to 2013</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>2028300288</v>
+        <v>2081556293</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
@@ -13678,7 +13494,7 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20102011</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20122013</t>
         </is>
       </c>
     </row>
@@ -13695,21 +13511,21 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Biotrade value and growth rates, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20122013</t>
+          <t>US_BiotradeMerch_20142015</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>From 2012 to 2013</t>
+          <t>From 2014 to 2015</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>1954366836</v>
+        <v>2085525371</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
@@ -13724,7 +13540,7 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20122013</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20142015</t>
         </is>
       </c>
     </row>
@@ -13741,21 +13557,21 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Biotrade value and growth rates, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20142015</t>
+          <t>US_BiotradeMerch_20162017</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>From 2014 to 2015</t>
+          <t>From 2016 to 2017</t>
         </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>1956042973</v>
+        <v>2083255752</v>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
@@ -13770,7 +13586,7 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20142015</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20162017</t>
         </is>
       </c>
     </row>
@@ -13787,21 +13603,21 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Biotrade value and growth rates, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20162017</t>
+          <t>US_BiotradeMerch_20182019</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>From 2016 to 2017</t>
+          <t>From 2018 to 2019</t>
         </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>1956496102</v>
+        <v>2046492014</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
@@ -13816,7 +13632,7 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20162017</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20182019</t>
         </is>
       </c>
     </row>
@@ -13833,21 +13649,21 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Biotrade value and growth rates, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20182019</t>
+          <t>US_BiotradeMerch_20202020</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>From 2018 to 2019</t>
+          <t>From 2020 to 2020</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>1923885736</v>
+        <v>999390394</v>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
@@ -13862,7 +13678,7 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20182019</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20202020</t>
         </is>
       </c>
     </row>
@@ -13879,21 +13695,21 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Biotrade value and growth rates, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20202021</t>
+          <t>US_BiotradeMerch_20212021</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>From 2020 to 2021</t>
+          <t>From 2021 to 2021</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>1903206552</v>
+        <v>1026527320</v>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
@@ -13908,7 +13724,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20202021</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20212021</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13741,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Biotrade value and growth rates, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -13939,7 +13755,7 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>977124670</v>
+        <v>1040823870</v>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
@@ -13971,7 +13787,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Biotrade value and growth rates, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -13985,7 +13801,7 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>974399399</v>
+        <v>1038282985</v>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
@@ -14017,7 +13833,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Biotrade value and growth rates, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -14031,7 +13847,7 @@
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>908444468</v>
+        <v>993411533</v>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
@@ -14058,17 +13874,17 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchGDPShare</t>
+          <t>US.BiotradeMerchShare</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Trade and biodiversity - Biotrade as percentage of Gross Domestic Product, annual (analytical)</t>
+          <t>Biotrade: Bilateral trade as percentage of total trade - Annual (analytical)</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>US_BioTradeMerchGDPShare</t>
+          <t>US_BiotradeMerchShare</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -14077,7 +13893,7 @@
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>21192</v>
+        <v>12702448</v>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
@@ -14085,14 +13901,14 @@
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>4</v>
+        <v>6810</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>4</v>
+        <v>6710</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BioTradeMerchGDPShare/US_BioTradeMerchGDPShare</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerchShare/US_BiotradeMerchShare</t>
         </is>
       </c>
     </row>
@@ -14104,17 +13920,17 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>US.BiotradeMerchShare</t>
+          <t>US.BioTradeMerchGDPShare</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Trade and biodiversity - Biotrade as percentage of total trade, annual (analytical)</t>
+          <t>Biotrade: Trade as percentage of Gross Domestic Product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerchShare</t>
+          <t>US_BioTradeMerchGDPShare</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -14123,7 +13939,7 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>12097505</v>
+        <v>21748</v>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
@@ -14131,14 +13947,14 @@
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>6623</v>
+        <v>4</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>6523</v>
+        <v>4</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerchShare/US_BiotradeMerchShare</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BioTradeMerchGDPShare/US_BioTradeMerchGDPShare</t>
         </is>
       </c>
     </row>
@@ -14155,7 +13971,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Revealed comparative advantage index, annual (analytical)</t>
+          <t>Biotrade: Revealed Comparative Advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -14201,7 +14017,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Product concentration indices of exports and imports, annual (analytical)</t>
+          <t>Biotrade: Product concentration index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -14247,7 +14063,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Trade and Biodiversity - Market concentration and structural change by product, annual (analytical)</t>
+          <t>Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -14707,7 +14523,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>ICT producing sector core indicators, annual</t>
+          <t>ICT producing sector: Workforce involved and value added - Annual</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -14748,17 +14564,17 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>US.IctGoodsValue</t>
+          <t>US.IctGoods</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Bilateral trade flows by ICT goods categories, annual</t>
+          <t>ICT goods: Bilateral trade by category - Annual</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>US_IctGoodsValue</t>
+          <t>US_IctGoods</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -14767,7 +14583,7 @@
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>91267142</v>
+        <v>115739203</v>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
@@ -14782,7 +14598,7 @@
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctGoodsValue/US_IctGoodsValue</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctGoods/US_IctGoods</t>
         </is>
       </c>
     </row>
@@ -14794,30 +14610,30 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>US.IctGoodsShare</t>
+          <t>US.IctUseLocation</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Share of ICT goods as percentage of total trade, annual</t>
+          <t>ICT use in business: Core indicators by location type - Annual</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>US_IctGoodsShare</t>
+          <t>US_IctUseLocation</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
-        <v>110565343</v>
+        <v>8295</v>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -14828,7 +14644,7 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctGoodsShare/US_IctGoodsShare</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseLocation/US_IctUseLocation</t>
         </is>
       </c>
     </row>
@@ -14840,26 +14656,26 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseLocation</t>
+          <t>US.IctUseEnterprSize</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Core indicators on ICT use in business by location type, annual</t>
+          <t>ICT use in business: Core indicators by enterprise size - Annual</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseLocation</t>
+          <t>US_IctUseEnterprSize</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2010 to 2025</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>8295</v>
+        <v>222567</v>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
@@ -14874,7 +14690,7 @@
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseLocation/US_IctUseLocation</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEnterprSize/US_IctUseEnterprSize</t>
         </is>
       </c>
     </row>
@@ -14886,17 +14702,17 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEnterprSize</t>
+          <t>US.IctUseEconActivity_Isic4</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Core indicators on ICT use in business by enterprise size class, annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 4) - Annual</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseEnterprSize</t>
+          <t>US_IctUseEconActivity_Isic4</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -14905,7 +14721,7 @@
         </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>222567</v>
+        <v>663946</v>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
@@ -14920,7 +14736,7 @@
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEnterprSize/US_IctUseEnterprSize</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity_Isic4/US_IctUseEconActivity_Isic4</t>
         </is>
       </c>
     </row>
@@ -14932,26 +14748,26 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity_Isic4</t>
+          <t>US.IctUseEconActivity</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Core indicators on ICT use in business by industrial classification of economic activity (ISIC Rev. 4), annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 3.1) - Annual</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseEconActivity_Isic4</t>
+          <t>US_IctUseEconActivity</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2025</t>
+          <t>From 2010 to 2021</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>663946</v>
+        <v>83239</v>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
@@ -14966,7 +14782,7 @@
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity_Isic4/US_IctUseEconActivity_Isic4</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity/US_IctUseEconActivity</t>
         </is>
       </c>
     </row>
@@ -14978,26 +14794,26 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity</t>
+          <t>US.DigitallyDeliverableServices</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Core indicators on ICT use in business by industrial classification of economic activity (ISIC Rev. 3.1), annual</t>
+          <t>Digitally deliverable services: Trade – Annual (analytical)</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseEconActivity</t>
+          <t>US_DigitallyDeliverableServices</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2021</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
-        <v>83239</v>
+        <v>1525091</v>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
@@ -15005,14 +14821,14 @@
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity/US_IctUseEconActivity</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.DigitallyDeliverableServices/US_DigitallyDeliverableServices</t>
         </is>
       </c>
     </row>
@@ -15024,26 +14840,26 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>US.DigitallyDeliverableServices</t>
+          <t>US.TradeServICT</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>International trade in digitally deliverable services, value, shares and growth, annual (analytical)</t>
+          <t>ICT services: Trade – Annual</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>US_DigitallyDeliverableServices</t>
+          <t>US_TradeServICT</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2005 to 2024</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
-        <v>1525091</v>
+        <v>141178</v>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
@@ -15051,14 +14867,14 @@
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>420</v>
+        <v>40</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>577</v>
+        <v>94</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.DigitallyDeliverableServices/US_DigitallyDeliverableServices</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServICT/US_TradeServICT</t>
         </is>
       </c>
     </row>
@@ -15070,26 +14886,26 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServICT</t>
+          <t>US.ECommerceTotal</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>International trade in ICT services, value, shares and growth, annual</t>
+          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>US_TradeServICT</t>
+          <t>US_ECommerceTotal</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 2012 to 2025</t>
         </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>141178</v>
+        <v>906006</v>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
@@ -15097,14 +14913,14 @@
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServICT/US_TradeServICT</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceTotal/US_ECommerceTotal</t>
         </is>
       </c>
     </row>
@@ -15116,26 +14932,26 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceTotal</t>
+          <t>US.ECommerceInternational</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
+          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>US_ECommerceTotal</t>
+          <t>US_ECommerceInternational</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>From 2012 to 2025</t>
+          <t>From 2015 to 2024</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>906006</v>
+        <v>139183</v>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
@@ -15150,7 +14966,7 @@
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceTotal/US_ECommerceTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceInternational/US_ECommerceInternational</t>
         </is>
       </c>
     </row>
@@ -15162,26 +14978,26 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceInternational</t>
+          <t>US.FTRI</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
+          <t>Frontier technology readiness index, annual (analytical)</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>US_ECommerceInternational</t>
+          <t>US_FTRI</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>From 2015 to 2024</t>
+          <t>From 2010 to 2023</t>
         </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>139183</v>
+        <v>62747</v>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
@@ -15189,14 +15005,14 @@
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceInternational/US_ECommerceInternational</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FTRI/US_FTRI</t>
         </is>
       </c>
     </row>
@@ -15208,26 +15024,26 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>US.FTRI</t>
+          <t>US.PopTotal</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Frontier technology readiness index, annual (analytical)</t>
+          <t>Population: Total - Annual</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>US_FTRI</t>
+          <t>US_PopTotal</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2023</t>
+          <t>From 1950 to 2050</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>62747</v>
+        <v>374021</v>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
@@ -15235,14 +15051,14 @@
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FTRI/US_FTRI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopTotal/US_PopTotal</t>
         </is>
       </c>
     </row>
@@ -15254,17 +15070,17 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>US.PopTotal</t>
+          <t>US.PopAgeStruct</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Population: Total - Annual</t>
+          <t>Population: Structure by gender and age group - Annual</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>US_PopTotal</t>
+          <t>US_PopAgeStruct</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -15273,7 +15089,7 @@
         </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>374021</v>
+        <v>12550832</v>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
@@ -15281,14 +15097,14 @@
         </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>101</v>
+        <v>6666</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>302</v>
+        <v>6666</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopTotal/US_PopTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopAgeStruct/US_PopAgeStruct</t>
         </is>
       </c>
     </row>
@@ -15300,17 +15116,17 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>US.PopAgeStruct</t>
+          <t>US.PopDependency</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Population: Structure by gender and age group - Annual</t>
+          <t>Population: Dependency ratios - Annual</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>US_PopAgeStruct</t>
+          <t>US_PopDependency</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -15319,7 +15135,7 @@
         </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>12550832</v>
+        <v>494161</v>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
@@ -15327,14 +15143,14 @@
         </is>
       </c>
       <c r="H119" s="5" t="n">
-        <v>6666</v>
+        <v>303</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>6666</v>
+        <v>303</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopAgeStruct/US_PopAgeStruct</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopDependency/US_PopDependency</t>
         </is>
       </c>
     </row>
@@ -15346,26 +15162,26 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>US.PopDependency</t>
+          <t>US.InclusiveGrowth</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Population: Dependency ratios - Annual</t>
+          <t>Inclusive Growth Index (IGI) (analytical)</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>US_PopDependency</t>
+          <t>US_InclusiveGrowth</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>From 1950 to 2050</t>
+          <t>From 2023 to 2023</t>
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>494161</v>
+        <v>4221</v>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
@@ -15373,14 +15189,14 @@
         </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopDependency/US_PopDependency</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.InclusiveGrowth/US_InclusiveGrowth</t>
         </is>
       </c>
     </row>
@@ -15392,26 +15208,26 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>US.InclusiveGrowth</t>
+          <t>US.Gender_DomesticValueAdded</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth Index (IGI) (analytical)</t>
+          <t>Domestic value added content in gross exports by sex and broad sector (analytical)</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>US_InclusiveGrowth</t>
+          <t>US_Gender_DomesticValueAdded</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>From 2023 to 2023</t>
+          <t>From 2000 to 2020</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>4221</v>
+        <v>97680</v>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
@@ -15426,7 +15242,7 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.InclusiveGrowth/US_InclusiveGrowth</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_DomesticValueAdded/US_Gender_DomesticValueAdded</t>
         </is>
       </c>
     </row>
@@ -15438,26 +15254,26 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_DomesticValueAdded</t>
+          <t>US.Gender_TradableIndustries</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Domestic value added content in gross exports by sex and broad sector (analytical)</t>
+          <t>Employment and average monthly earnings in tradable and non-tradable industries (analytical)</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>US_Gender_DomesticValueAdded</t>
+          <t>US_Gender_TradableIndustries</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2020</t>
+          <t>From 2000 to 2023</t>
         </is>
       </c>
       <c r="F122" s="5" t="n">
-        <v>97680</v>
+        <v>176441</v>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
@@ -15465,14 +15281,14 @@
         </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_DomesticValueAdded/US_Gender_DomesticValueAdded</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_TradableIndustries/US_Gender_TradableIndustries</t>
         </is>
       </c>
     </row>
@@ -15484,26 +15300,26 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_TradableIndustries</t>
+          <t>US.SDG_LULFRG</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Employment and average monthly earnings in tradable and non-tradable industries (analytical)</t>
+          <t>Indicator 9.1.2: Freight loaded and unloaded, maritime transport (metric tons) [IS_RDP_LULFRG]</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>US_Gender_TradableIndustries</t>
+          <t>US_SDG_LULFRG</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2023</t>
+          <t>From 2000 to 2024</t>
         </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>176441</v>
+        <v>46857</v>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
@@ -15511,14 +15327,14 @@
         </is>
       </c>
       <c r="H123" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_TradableIndustries/US_Gender_TradableIndustries</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_LULFRG/US_SDG_LULFRG</t>
         </is>
       </c>
     </row>
@@ -15530,26 +15346,26 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>US.SDG_LULFRG</t>
+          <t>US.SDG_PORFVOL</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2, Freight loaded and unloaded, maritime transport (metric tons) [IS_RDP_LULFRG]</t>
+          <t>Indicator 9.1.2: Container port traffic, maritime transport (twenty-foot equivalent units – TEUs) [IS_RDP_PORFVOL]</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>US_SDG_LULFRG</t>
+          <t>US_SDG_PORFVOL</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F124" s="5" t="n">
-        <v>46857</v>
+        <v>15386</v>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
@@ -15557,14 +15373,14 @@
         </is>
       </c>
       <c r="H124" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_LULFRG/US_SDG_LULFRG</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_PORFVOL/US_SDG_PORFVOL</t>
         </is>
       </c>
     </row>
@@ -15576,26 +15392,26 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>US.SDG_PORFVOL</t>
+          <t>US.IFF_TradeMisinvoicing</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2, Container port traffic, maritime transport (twenty-foot equivalent units – TEUs) [IS_RDP_PORFVOL]</t>
+          <t>Indicator 16.4.1: Trade misinvoicing illicit financial flows - Annual</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>US_SDG_PORFVOL</t>
+          <t>US_IFF_TradeMisinvoicing</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2011 to 2024</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
-        <v>15386</v>
+        <v>3342</v>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
@@ -15603,14 +15419,14 @@
         </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_PORFVOL/US_SDG_PORFVOL</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IFF_TradeMisinvoicing/US_IFF_TradeMisinvoicing</t>
         </is>
       </c>
     </row>
@@ -15622,26 +15438,26 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>US.IFF_TradeMisinvoicing</t>
+          <t>US.IFF_CrimesRelated</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Indicator 16.4.1: Trade misinvoicing illicit financial flows, IFFs - Annual</t>
+          <t>Indicator 16.4.1: Crime-related illicit financial flows - Annual</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>US_IFF_TradeMisinvoicing</t>
+          <t>US_IFF_CrimesRelated</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>From 2011 to 2024</t>
+          <t>From 2015 to 2025</t>
         </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>3342</v>
+        <v>2046</v>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
@@ -15655,52 +15471,6 @@
         <v>0</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IFF_TradeMisinvoicing/US_IFF_TradeMisinvoicing</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>UNCTADstat - UNCTAD</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>US.IFF_CrimesRelated</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>Indicator 16.4.1: Crime-related illicit financial flows, IFFs - Annual</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>US_IFF_CrimesRelated</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>From 2015 to 2025</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>2046</v>
-      </c>
-      <c r="G127" s="4" t="inlineStr">
-        <is>
-          <t>Procesado</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
         <is>
           <t>https://unctadstat-api.unctad.org/bulkdownload/US.IFF_CrimesRelated/US_IFF_CrimesRelated</t>
         </is>
@@ -15786,7 +15556,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15869,7 +15639,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -15879,7 +15649,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -15889,7 +15659,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -15899,7 +15669,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>85389</v>
+        <v>84770</v>
       </c>
     </row>
     <row r="20">

--- a/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
+++ b/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>

--- a/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
+++ b/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
@@ -1289,20 +1289,20 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>US.FdiFlowsStock</t>
+          <t>US.GoodsAndServicesBpm6</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1912</v>
+        <v>2210</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Foreign direct investment: Inward and outward flows and stock, annual</t>
+          <t>Balance of payments: Goods and services trade - Annual</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Foreign direct investment</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>foreign, direct, investment, flow, stock, inward, outward, FDI</t>
+          <t>trade, goods, services</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>2025-09-01T06:17:00</t>
+          <t>2026-04-09T07:52:00</t>
         </is>
       </c>
       <c r="J13" s="5" t="n">
@@ -1330,19 +1330,19 @@
         <v>0</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>370935</v>
+        <v>362860</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>280</v>
+        <v>174</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -1385,15 +1385,15 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>US.GoodsAndServicesBpm6</t>
+          <t>US.GoodsAndServBalanceBpm6</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Goods and services (BPM6): Exports and imports of goods and services, annual</t>
+          <t>Balance of payments: Goods and services trade balance indicators - Annual</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>trade, goods, services</t>
+          <t>Trade, indicators, balances</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1426,10 +1426,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>362860</v>
+        <v>305732</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
@@ -1481,15 +1481,15 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>US.GoodsAndServBalanceBpm6</t>
+          <t>US.GoodsAndServTradeOpennessBpm6</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Goods and services (BPM6): Trade balance indicators, annual</t>
+          <t>Balance of payments: Goods and services trade openness indicators - Annual</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Trade, indicators, balances</t>
+          <t>Trade, Indicators, Exports, Imports</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>305732</v>
+        <v>859488</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -1577,20 +1577,20 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>US.GoodsAndServTradeOpennessBpm6</t>
+          <t>US.FdiFlowsStock</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2209</v>
+        <v>2559</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Goods and services (BPM6): Trade openness indicators, annual</t>
+          <t>Foreign direct investment: Inward and outward flows and stock, annual</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>Foreign direct investment</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Trade, Indicators, Exports, Imports</t>
+          <t>foreign, direct, investment, flow, stock, inward, outward, FDI</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09T07:52:00</t>
+          <t>2026-08-17T12:15:00</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
@@ -1618,19 +1618,19 @@
         <v>0</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>859488</v>
+        <v>676265</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>360</v>
+        <v>576</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>2511</v>
+        <v>2570</v>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T13:17:00</t>
+          <t>2026-08-17T07:42:00</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
@@ -6922,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>66643</v>
+        <v>66860</v>
       </c>
       <c r="N72" s="5" t="n">
         <v>0</v>
@@ -11625,7 +11625,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Goods and services (BPM6): Exports and imports of goods and services, annual</t>
+          <t>Balance of payments: Goods and services trade - Annual</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Goods and services (BPM6): Trade balance indicators, annual</t>
+          <t>Balance of payments: Goods and services trade balance indicators - Annual</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Goods and services (BPM6): Trade openness indicators, annual</t>
+          <t>Balance of payments: Goods and services trade openness indicators - Annual</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -11819,11 +11819,11 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>From 1990 to 2024</t>
+          <t>From 1990 to 2025</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>370935</v>
+        <v>676265</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
@@ -11831,10 +11831,10 @@
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>280</v>
+        <v>576</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>66643</v>
+        <v>66860</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -15669,7 +15669,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>84770</v>
+        <v>85066</v>
       </c>
     </row>
     <row r="20">

--- a/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
+++ b/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>546</v>
+        <v>2553</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>2023-07-18T16:51:00</t>
+          <t>2026-08-28T08:04:00</t>
         </is>
       </c>
       <c r="J10" s="5" t="n">
@@ -1042,10 +1042,10 @@
         <v>0</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>102323</v>
+        <v>81423</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -2249,15 +2249,15 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchProdConcent</t>
+          <t>US.BioTradeMerchGDPShare</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2120</v>
+        <v>2513</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Product concentration index - Annual (analytical)</t>
+          <t>Biotrade: Trade as percentage of Gross Domestic Product - Annual (analytical)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Export, import, merchandise, trade, product concentration, biotrade, biodiversity</t>
+          <t>Export, import, share, GDP, merchandise, trade, biotrade, biodiversity</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>2025-11-28T16:02:00</t>
+          <t>2026-07-20T06:30:00</t>
         </is>
       </c>
       <c r="J23" s="5" t="n">
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>34933</v>
+        <v>21748</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>US.BiotradeMerchRCA</t>
+          <t>US.BioTradeMerchProdConcent</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Revealed Comparative Advantage index - Annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Product concentration index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Merchandise biotrade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Export, import, merchandise, trade, Revealed Comparative Advantage, RCA, biotrade, biodiversity</t>
+          <t>Export, import, merchandise, trade, product concentration, biotrade, biodiversity</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2386,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>20785250</v>
+        <v>34933</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>2635</v>
+        <v>8</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
@@ -2441,20 +2441,20 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchGDPShare</t>
+          <t>US.BiotradeMerchRCA</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2513</v>
+        <v>2121</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Trade as percentage of Gross Domestic Product - Annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Revealed Comparative Advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>Merchandise biotrade</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Export, import, share, GDP, merchandise, trade, biotrade, biodiversity</t>
+          <t>Export, import, merchandise, trade, Revealed Comparative Advantage, RCA, biotrade, biodiversity</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20T06:30:00</t>
+          <t>2025-11-28T16:02:00</t>
         </is>
       </c>
       <c r="J25" s="5" t="n">
@@ -2482,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>21748</v>
+        <v>20785250</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>4</v>
+        <v>2635</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1973</v>
+        <v>2481</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>2025-11-04T13:38:00</t>
+          <t>2026-08-25T13:15:00</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
@@ -3346,10 +3346,10 @@
         <v>0</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>8636215</v>
+        <v>8931393</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>7519</v>
+        <v>7772</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q34" s="4" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
+          <t>Port liner shipping connectivity index, quarterly (analytical)</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -10669,11 +10669,11 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2024</t>
+          <t>From 1995 to 2025</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>8636215</v>
+        <v>8931393</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -10681,10 +10681,10 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>7519</v>
+        <v>7772</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>7519</v>
+        <v>7772</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -11957,11 +11957,11 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>The whole period</t>
+          <t>From 1980 to 2025</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>102323</v>
+        <v>81423</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
@@ -11969,10 +11969,10 @@
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
+          <t>Port liner shipping connectivity index, quarterly (analytical)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Revealed Comparative Advantage index - Annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Revealed Comparative Advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Product concentration index - Annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Product concentration index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -15669,7 +15669,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>85066</v>
+        <v>85325</v>
       </c>
     </row>
     <row r="20">

--- a/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
+++ b/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
@@ -1001,15 +1001,15 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>US.Cpi_A</t>
+          <t>US.ExchangeRateCrosstab</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2553</v>
+        <v>2362</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Consumer price indices, annual (analytical)</t>
+          <t>Exchange rates: Currency cross rates - Annual</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Consumer Price Indices, CPI</t>
+          <t>exchange, rate, currency</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T08:04:00</t>
+          <t>2026-05-29T14:04:00</t>
         </is>
       </c>
       <c r="J10" s="5" t="n">
@@ -1042,19 +1042,19 @@
         <v>0</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>81423</v>
+        <v>18056762</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>91</v>
+        <v>23205</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -1097,15 +1097,15 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>US.ExchangeRateCrosstab</t>
+          <t>US.Cpi_A</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2362</v>
+        <v>2553</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Exchange rates: Currency cross rates - Annual</t>
+          <t>Inflation: Consumer price index - Annual</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>exchange, rate, currency</t>
+          <t>Consumer Price Indices, CPI</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29T14:04:00</t>
+          <t>2026-08-28T08:04:00</t>
         </is>
       </c>
       <c r="J11" s="5" t="n">
@@ -1138,19 +1138,19 @@
         <v>0</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>18056762</v>
+        <v>81423</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>23205</v>
+        <v>91</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Balance of payments, Current account balance, annual</t>
+          <t>Balance of payments: Current account balance - Annual</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2210</v>
+        <v>2575</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09T07:52:00</t>
+          <t>2026-09-01T06:44:00</t>
         </is>
       </c>
       <c r="J13" s="5" t="n">
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>362860</v>
+        <v>380006</v>
       </c>
       <c r="N13" s="5" t="n">
         <v>174</v>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2211</v>
+        <v>2576</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09T07:52:00</t>
+          <t>2026-09-01T06:44:00</t>
         </is>
       </c>
       <c r="J14" s="5" t="n">
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>305732</v>
+        <v>321969</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>180</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2209</v>
+        <v>2574</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09T07:52:00</t>
+          <t>2026-09-01T06:44:00</t>
         </is>
       </c>
       <c r="J15" s="5" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>859488</v>
+        <v>903326</v>
       </c>
       <c r="N15" s="5" t="n">
         <v>360</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>International trade in creative services: estimates for individual economies (analytical)</t>
+          <t>Creative services: Trade - Annual (analytical)</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>2481</v>
+        <v>2589</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T13:15:00</t>
+          <t>2026-06-30T07:17:00</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Port liner shipping connectivity index, quarterly (analytical)</t>
+          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>1895</v>
+        <v>2582</v>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>2025-08-04T07:52:00</t>
+          <t>2026-09-04T12:05:00</t>
         </is>
       </c>
       <c r="J82" s="5" t="n">
@@ -7802,7 +7802,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>29490920</v>
+        <v>33181670</v>
       </c>
       <c r="N82" s="5" t="n">
         <v>0</v>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>1894</v>
+        <v>2581</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>2025-08-04T07:52:00</t>
+          <t>2026-09-04T12:05:00</t>
         </is>
       </c>
       <c r="J83" s="5" t="n">
@@ -7890,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>81455754</v>
+        <v>90879049</v>
       </c>
       <c r="N83" s="5" t="n">
         <v>0</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>1896</v>
+        <v>2583</v>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>2025-08-04T07:52:00</t>
+          <t>2026-09-04T12:05:00</t>
         </is>
       </c>
       <c r="J84" s="5" t="n">
@@ -7978,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>49942922</v>
+        <v>55831373</v>
       </c>
       <c r="N84" s="5" t="n">
         <v>0</v>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Creative goods matrix, annual (analytical)</t>
+          <t>Creative goods: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Creative goods matrix, growth rates, annual (analytical)</t>
+          <t>Creative goods: Bilateral trade by product group - Growth rates - Annual (analytical)</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Creative services exports of selected groups of economies (analytical)</t>
+          <t>Creative services: exports of selected groups of economies - Annual (analytical)</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>2507</v>
+        <v>2592</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T13:43:00</t>
+          <t>2026-07-14T07:18:00</t>
         </is>
       </c>
       <c r="J91" s="5" t="n">
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>2480</v>
+        <v>2588</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08T10:38:00</t>
+          <t>2026-06-30T07:17:00</t>
         </is>
       </c>
       <c r="J92" s="5" t="n">
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>2482</v>
+        <v>2590</v>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08T10:38:00</t>
+          <t>2026-06-30T07:17:00</t>
         </is>
       </c>
       <c r="J94" s="5" t="n">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade price index – Quarterly (analytical)</t>
+          <t>Merchandise: Trade price index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade price index – Quarterly (analytical)</t>
+          <t>Merchandise: Trade price index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -10654,26 +10654,26 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>US.RCA</t>
+          <t>US.MerchTheilIndices</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Revealed Comparative Advantage index - Annual (analytical)</t>
+          <t>Merchandise: Theil concentration indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>US_RCA</t>
+          <t>US_MerchTheilIndices</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2025</t>
+          <t>From 1995 to 2024</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>8931393</v>
+        <v>353039</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -10681,14 +10681,14 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>7772</v>
+        <v>180</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>7772</v>
+        <v>180</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.RCA/US_RCA</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.MerchTheilIndices/US_MerchTheilIndices</t>
         </is>
       </c>
     </row>
@@ -10700,26 +10700,26 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>US.Tariff</t>
+          <t>US.RCA</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Import tariff rates - Annual</t>
+          <t>Merchandise: Revealed Comparative Advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>US_Tariff</t>
+          <t>US_RCA</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2023</t>
+          <t>From 1995 to 2025</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1484011</v>
+        <v>8931393</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
@@ -10727,14 +10727,14 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>1084</v>
+        <v>7772</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>2168</v>
+        <v>7772</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Tariff/US_Tariff</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.RCA/US_RCA</t>
         </is>
       </c>
     </row>
@@ -10746,26 +10746,26 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>US.MerchTheilIndices</t>
+          <t>US.Tariff</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Theil concentration indices - Annual (analytical)</t>
+          <t>Merchandise: Import tariff rates - Annual</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>US_MerchTheilIndices</t>
+          <t>US_Tariff</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2024</t>
+          <t>From 2000 to 2023</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>353039</v>
+        <v>1484011</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
@@ -10773,14 +10773,14 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>180</v>
+        <v>1084</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>180</v>
+        <v>2168</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.MerchTheilIndices/US_MerchTheilIndices</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Tariff/US_Tariff</t>
         </is>
       </c>
     </row>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Creative goods matrix, annual (analytical)</t>
+          <t>Creative goods: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Creative goods matrix, growth rates, annual (analytical)</t>
+          <t>Creative goods: Bilateral trade by product group - Growth rates - Annual (analytical)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>International trade in creative services: estimates for individual economies (analytical)</t>
+          <t>Creative services: Trade - Annual (analytical)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Creative services exports of selected groups of economies (analytical)</t>
+          <t>Creative services: exports of selected groups of economies - Annual (analytical)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -11635,11 +11635,11 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 2005 to 2025</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>362860</v>
+        <v>380006</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>174</v>
@@ -11681,11 +11681,11 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 2005 to 2025</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>305732</v>
+        <v>321969</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>180</v>
@@ -11727,11 +11727,11 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 2005 to 2025</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>859488</v>
+        <v>903326</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>360</v>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Balance of payments, Current account balance, annual</t>
+          <t>Balance of payments: Current account balance - Annual</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Consumer price indices, annual (analytical)</t>
+          <t>Inflation: Consumer price index - Annual</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Port liner shipping connectivity index, quarterly (analytical)</t>
+          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -14257,11 +14257,11 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2023</t>
+          <t>From 2005 to 2024</t>
         </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>81455754</v>
+        <v>90879049</v>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
@@ -14303,11 +14303,11 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2023</t>
+          <t>From 2005 to 2024</t>
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>29490920</v>
+        <v>33181670</v>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
@@ -14349,11 +14349,11 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2023</t>
+          <t>From 2005 to 2024</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>49942922</v>
+        <v>55831373</v>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
